--- a/outputs/019f8a1b-d701-7662-81fe-3741d3277c70/typed_evidence_ref_generalization_review_64.xlsx
+++ b/outputs/019f8a1b-d701-7662-81fe-3741d3277c70/typed_evidence_ref_generalization_review_64.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2693ef17a95b4178"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="R44d27deb1a6c4b67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="3" r:id="R650b0c9e439e4d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" r:id="R1d6426ab78e14b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9e349795f6134cb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="R1f9370a0fc084020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="3" r:id="R9dbf7b115bd54b15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" r:id="R30a8b18cccee4edb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EvidenceUnitsTable" displayName="EvidenceUnitsTable" ref="A1:O98" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EvidenceUnitsTable" displayName="EvidenceUnitsTable" ref="A1:O99" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="Slot"/>
     <x:tableColumn id="2" name="Requirement ID"/>
@@ -534,7 +534,7 @@
         <x:v>정확 근거 단위</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -946,7 +946,7 @@
         <x:v>sibling_relation</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>6월 12일 세리아 특별 상점에서 종말의 계시 500개 상자와 피로도 30 회복의 비약은 각각 몇 개씩 팔았어?</x:v>
+        <x:v>세리아와 함께한 20주년 선물 5주차 추첨에서 그래픽카드와 키보드·장패드는 각각 몇 개였어?</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
         <x:v>full_answer</x:v>
@@ -961,14 +961,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>revelation_box_quantity: [Event]종말의 계시 500개 상자 / sale_quantity / number / [2]
-fatigue_potion_quantity: 피로도 30 회복의 비약 / sale_quantity / number / [2]</x:v>
+        <x:v>graphics_card_quantity: [20th special]던전 앤 그래픽카드 / drawing_goods_quantity / number / [4]
+keyboard_mousepad_quantity: [20th special]20주년 키보드 + 장패드 / drawing_goods_quantity / number / [12]</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str">
-        <x:v>6/12(금) 세리아 특별 상점 물품 판매 안내</x:v>
+        <x:v>[5주차] 세리아와 함께한 20주년 선물 추첨 당첨자 발표</x:v>
       </x:c>
       <x:c r="K4" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/notice/2927710</x:v>
+        <x:v>https://df.nexon.com/community/news/notice/2924996</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
         <x:v>draft_complete_pending_human_review</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>sibling_relation</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 아바타 풀세트 상자와 웨딩 보너스 상자는 각각 언제 삭제돼?</x:v>
+        <x:v>썸머 특제 피로도 30 회복의 비약은 1회차와 7회차에 각각 얼마였어?</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
         <x:v>full_answer</x:v>
@@ -1735,14 +1735,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I20" s="11" t="str">
-        <x:v>avatar_box_deletion: 2026 아라드 패스 웨딩 아바타 풀세트 상자 / deletion_at / datetime / ["2026-08-13T06:00:00+09:00"]
-bonus_box_deletion: 2026 아라드 패스 웨딩 보너스 상자 / deletion_at / datetime / ["2026-08-13T06:00:00+09:00"]</x:v>
+        <x:v>first_purchase_price: [세라샵]2026 썸머 특제 피로도 30 회복의 비약 NO.1 / price / currency / [{"amount":500,"unit":"세라"}]
+seventh_purchase_price: [세라샵]2026 썸머 특제 피로도 30 회복의 비약 NO.7 / price / currency / [{"amount":2000,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 아바타 콤보 상자</x:v>
+        <x:v>썸머 특제 피로도 30 회복의 비약</x:v>
       </x:c>
       <x:c r="K20" s="11" t="str">
-        <x:v>https://df.nexon.com/pg/weddingcombo</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/626</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
         <x:v>draft_complete_pending_human_review</x:v>
@@ -2012,7 +2012,7 @@
         <x:v>temporal_role</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>트레이드 가이드는 언제 업데이트됐어?</x:v>
+        <x:v>던파ON 출석체크는 매일 몇 시에 갱신되고, 보상 교환의 1주 기준은 언제야?</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
         <x:v>full_answer</x:v>
@@ -2024,16 +2024,17 @@
         <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str">
-        <x:v>guide_updated_at: 트레이드 가이드 / updated_at / date / ["2026-01-05"]</x:v>
+        <x:v>daily_reset_time: 던파ON 출석체크 / daily_reset_time / enum / ["06:00"]
+weekly_reset_at: 던파ON 보상 교환 / weekly_reset_at / enum / ["매주 목요일 오전 6시"]</x:v>
       </x:c>
       <x:c r="J26" s="11" t="str">
-        <x:v>트레이드</x:v>
+        <x:v>던파ON 포인트 교환소</x:v>
       </x:c>
       <x:c r="K26" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1286</x:v>
+        <x:v>https://df.nexon.com/guide?no=1326</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
         <x:v>draft_complete_pending_human_review</x:v>
@@ -3988,7 +3989,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R643adc8cfe1d484f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8e765ffcda243cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4161,46 +4162,46 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>revelation_box_quantity</x:v>
+        <x:v>graphics_card_quantity</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>[Event]종말의 계시 500개 상자</x:v>
+        <x:v>[20th special]던전 앤 그래픽카드</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>sale_quantity</x:v>
+        <x:v>drawing_goods_quantity</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>number</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>[2]</x:v>
+        <x:v>[4]</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>[Event]종말의 계시 500개 상자 2개</x:v>
+        <x:v>[20th special]던전 앤 그래픽카드 (4개)</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str">
-        <x:v>6/12(금) 세리아 특별 상점 물품 판매 안내</x:v>
+        <x:v>[5주차] 세리아와 함께한 20주년 선물 추첨 당첨자 발표</x:v>
       </x:c>
       <x:c r="K4" s="11" t="str">
-        <x:v>document_sha256_02b647e98136fec7c3e8365815de0f40fafb52a478b80d4fb0e32a8033b142e6</x:v>
+        <x:v>document_sha256_0cc780d0a8897dbfb8946825378b71fdb10ddddc8b0ef5dda6e34722ba6f44cd</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>chunk_sha256_5ac51535e2805865522412deac4cfb565e9ad9faa4e57a67db855d69dcfbaf73</x:v>
+        <x:v>chunk_sha256_eac72b4d5bb920cb99dc3530d5f8607122fa39d26e361afcc93269d1daa3fd8c</x:v>
       </x:c>
       <x:c r="M4" s="11" t="n">
-        <x:v>150</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="N4" s="11" t="n">
-        <x:v>174</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="O4" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/notice/2927710</x:v>
+        <x:v>https://df.nexon.com/community/news/notice/2924996</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -4208,46 +4209,46 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>fatigue_potion_quantity</x:v>
+        <x:v>keyboard_mousepad_quantity</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>피로도 30 회복의 비약</x:v>
+        <x:v>[20th special]20주년 키보드 + 장패드</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>sale_quantity</x:v>
+        <x:v>drawing_goods_quantity</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>number</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>[2]</x:v>
+        <x:v>[12]</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>피로도 30 회복의 비약 2개</x:v>
+        <x:v>[20th special]20주년 키보드 + 장패드 (12개)</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str">
-        <x:v>6/12(금) 세리아 특별 상점 물품 판매 안내</x:v>
+        <x:v>[5주차] 세리아와 함께한 20주년 선물 추첨 당첨자 발표</x:v>
       </x:c>
       <x:c r="K5" s="11" t="str">
-        <x:v>document_sha256_02b647e98136fec7c3e8365815de0f40fafb52a478b80d4fb0e32a8033b142e6</x:v>
+        <x:v>document_sha256_0cc780d0a8897dbfb8946825378b71fdb10ddddc8b0ef5dda6e34722ba6f44cd</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>chunk_sha256_5ac51535e2805865522412deac4cfb565e9ad9faa4e57a67db855d69dcfbaf73</x:v>
+        <x:v>chunk_sha256_eac72b4d5bb920cb99dc3530d5f8607122fa39d26e361afcc93269d1daa3fd8c</x:v>
       </x:c>
       <x:c r="M5" s="11" t="n">
-        <x:v>175</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="N5" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="O5" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/notice/2927710</x:v>
+        <x:v>https://df.nexon.com/community/news/notice/2924996</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
@@ -5183,46 +5184,46 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>avatar_box_deletion</x:v>
+        <x:v>first_purchase_price</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 아바타 풀세트 상자</x:v>
+        <x:v>[세라샵]2026 썸머 특제 피로도 30 회복의 비약 NO.1</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>deletion_at</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>datetime</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str">
-        <x:v>["2026-08-13T06:00:00+09:00"]</x:v>
+        <x:v>[{"amount":500,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 아바타 풀세트 상자(교환가능)는 2026년 8월 13일 06시 일괄 삭제됩니다.</x:v>
+        <x:v>| 1회차 | | [세라샵]2026 썸머 특제 피로도 30 회복의 비약 NO.1 | 500세라 |</x:v>
       </x:c>
       <x:c r="J26" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 아바타 콤보 상자</x:v>
+        <x:v>썸머 특제 피로도 30 회복의 비약</x:v>
       </x:c>
       <x:c r="K26" s="11" t="str">
-        <x:v>document_sha256_700f371b436804a6a8481b26f67661daa4944425ae70d02a8b882d9d13aacffe</x:v>
+        <x:v>document_sha256_6bc3e01a673d4f734721e1291a8f5efff8e55e90114fd57981b5b73226afe888</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>chunk_sha256_c16ee037bdd7f570034db3a4b3577d033682de86caff4d039a5453dca56548fc</x:v>
+        <x:v>chunk_sha256_94379e20d73b98a29c63d351a0ed78a8551675f120ad178f57a1598091933f19</x:v>
       </x:c>
       <x:c r="M26" s="11" t="n">
-        <x:v>291</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="N26" s="11" t="n">
-        <x:v>350</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="O26" s="11" t="str">
-        <x:v>https://df.nexon.com/pg/weddingcombo</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/626</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
@@ -5230,46 +5231,46 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>bonus_box_deletion</x:v>
+        <x:v>seventh_purchase_price</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 보너스 상자</x:v>
+        <x:v>[세라샵]2026 썸머 특제 피로도 30 회복의 비약 NO.7</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>deletion_at</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>datetime</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str">
-        <x:v>["2026-08-13T06:00:00+09:00"]</x:v>
+        <x:v>[{"amount":2000,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H27" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 보너스 상자(교환가능)는 2026년 8월 13일 06시 일괄 삭제됩니다.</x:v>
+        <x:v>| 7회차 | | [세라샵]2026 썸머 특제 피로도 30 회복의 비약 NO.7 | 2,000세라 |</x:v>
       </x:c>
       <x:c r="J27" s="11" t="str">
-        <x:v>2026 아라드 패스 웨딩 아바타 콤보 상자</x:v>
+        <x:v>썸머 특제 피로도 30 회복의 비약</x:v>
       </x:c>
       <x:c r="K27" s="11" t="str">
-        <x:v>document_sha256_700f371b436804a6a8481b26f67661daa4944425ae70d02a8b882d9d13aacffe</x:v>
+        <x:v>document_sha256_6bc3e01a673d4f734721e1291a8f5efff8e55e90114fd57981b5b73226afe888</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>chunk_sha256_023c9bec1b3d61c320ce89ca2ac5a918b96c57b3850de725ab4e0a4f6e5032b8</x:v>
+        <x:v>chunk_sha256_94379e20d73b98a29c63d351a0ed78a8551675f120ad178f57a1598091933f19</x:v>
       </x:c>
       <x:c r="M27" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>1039</x:v>
       </x:c>
       <x:c r="N27" s="11" t="n">
-        <x:v>175</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="O27" s="11" t="str">
-        <x:v>https://df.nexon.com/pg/weddingcombo</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/626</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
@@ -5694,101 +5695,101 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B37" s="11" t="str">
-        <x:v>guide_updated_at</x:v>
+        <x:v>daily_reset_time</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>트레이드 가이드</x:v>
+        <x:v>던파ON 출석체크</x:v>
       </x:c>
       <x:c r="E37" s="11" t="str">
-        <x:v>updated_at</x:v>
+        <x:v>daily_reset_time</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>date</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="G37" s="11" t="str">
-        <x:v>["2026-01-05"]</x:v>
+        <x:v>["06:00"]</x:v>
       </x:c>
       <x:c r="H37" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" s="11" t="str">
-        <x:v>이 문서는 2026-01-05에 업데이트 되었습니다.</x:v>
+        <x:v>출석체크는 매일 06시를 기준으로 갱신됩니다.</x:v>
       </x:c>
       <x:c r="J37" s="11" t="str">
-        <x:v>트레이드</x:v>
+        <x:v>던파ON 포인트 교환소</x:v>
       </x:c>
       <x:c r="K37" s="11" t="str">
-        <x:v>document_sha256_15bd7d49ee6067b02b600bb64ea81bf9e9272b5c70820eb819bcf224cde1942a</x:v>
+        <x:v>document_sha256_b7bc843187a068ea6f4781b051c77e872a203cbe726dd21f09b10ce9e52e0c25</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
-        <x:v>chunk_sha256_10bd08402e9be2679be178b8422de4d86ae8856ff317923762d10e29112a661b</x:v>
+        <x:v>chunk_sha256_ecbd48044df650c1df8ce923008c63f5ecf780be047fd761ca8f9518369f015e</x:v>
       </x:c>
       <x:c r="M37" s="11" t="n">
-        <x:v>584</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="N37" s="11" t="n">
-        <x:v>613</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="O37" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1286</x:v>
+        <x:v>https://df.nexon.com/guide?no=1326</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="54" customHeight="1">
       <x:c r="A38" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B38" s="11" t="str">
-        <x:v>cross_channel_trade</x:v>
+        <x:v>weekly_reset_at</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>트레이드</x:v>
+        <x:v>던파ON 보상 교환</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
-        <x:v>can_request_cross_channel</x:v>
+        <x:v>weekly_reset_at</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>boolean</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="G38" s="11" t="str">
-        <x:v>[false]</x:v>
+        <x:v>["매주 목요일 오전 6시"]</x:v>
       </x:c>
       <x:c r="H38" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I38" s="11" t="str">
-        <x:v>다른 채널에 접속한 캐릭터에게는 트레이드를 신청할 수 없습니다.</x:v>
+        <x:v>1주 기준은 매주 목요일 오전 6시</x:v>
       </x:c>
       <x:c r="J38" s="11" t="str">
-        <x:v>트레이드</x:v>
+        <x:v>던파ON 포인트 교환소</x:v>
       </x:c>
       <x:c r="K38" s="11" t="str">
-        <x:v>document_sha256_15bd7d49ee6067b02b600bb64ea81bf9e9272b5c70820eb819bcf224cde1942a</x:v>
+        <x:v>document_sha256_b7bc843187a068ea6f4781b051c77e872a203cbe726dd21f09b10ce9e52e0c25</x:v>
       </x:c>
       <x:c r="L38" s="11" t="str">
-        <x:v>chunk_sha256_10bd08402e9be2679be178b8422de4d86ae8856ff317923762d10e29112a661b</x:v>
+        <x:v>chunk_sha256_6e8d119cb7eb75d41cbb6524549de7f332d4f962085797df8b9d68e1fad174be</x:v>
       </x:c>
       <x:c r="M38" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="N38" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="O38" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1286</x:v>
+        <x:v>https://df.nexon.com/guide?no=1326</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
       <x:c r="A39" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B39" s="11" t="str">
-        <x:v>base_fee</x:v>
+        <x:v>cross_channel_trade</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
         <x:v>supported</x:v>
@@ -5797,19 +5798,19 @@
         <x:v>트레이드</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>base_fee</x:v>
+        <x:v>can_request_cross_channel</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>percentage</x:v>
+        <x:v>boolean</x:v>
       </x:c>
       <x:c r="G39" s="11" t="str">
-        <x:v>[3]</x:v>
+        <x:v>[false]</x:v>
       </x:c>
       <x:c r="H39" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I39" s="11" t="str">
-        <x:v>트레이드 시에는 3%의 수수료가 부과됩니다.</x:v>
+        <x:v>다른 채널에 접속한 캐릭터에게는 트레이드를 신청할 수 없습니다.</x:v>
       </x:c>
       <x:c r="J39" s="11" t="str">
         <x:v>트레이드</x:v>
@@ -5818,13 +5819,13 @@
         <x:v>document_sha256_15bd7d49ee6067b02b600bb64ea81bf9e9272b5c70820eb819bcf224cde1942a</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str">
-        <x:v>chunk_sha256_062cf0c88225fa6fb860cd0cb4a38b2adce8b4a8560d1cf70f01eb0298742463</x:v>
+        <x:v>chunk_sha256_10bd08402e9be2679be178b8422de4d86ae8856ff317923762d10e29112a661b</x:v>
       </x:c>
       <x:c r="M39" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N39" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="O39" s="11" t="str">
         <x:v>https://df.nexon.com/guide?no=1286</x:v>
@@ -5835,28 +5836,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B40" s="11" t="str">
-        <x:v>equipment_extra_fee</x:v>
+        <x:v>base_fee</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>장비류 아이템 트레이드</x:v>
+        <x:v>트레이드</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>additional_fee</x:v>
+        <x:v>base_fee</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
         <x:v>percentage</x:v>
       </x:c>
       <x:c r="G40" s="11" t="str">
-        <x:v>[2]</x:v>
+        <x:v>[3]</x:v>
       </x:c>
       <x:c r="H40" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I40" s="11" t="str">
-        <x:v>장비류 아이템인 경우에는 2%의 수수료가 추가로 부과됩니다.(총 5%)</x:v>
+        <x:v>트레이드 시에는 3%의 수수료가 부과됩니다.</x:v>
       </x:c>
       <x:c r="J40" s="11" t="str">
         <x:v>트레이드</x:v>
@@ -5868,10 +5869,10 @@
         <x:v>chunk_sha256_062cf0c88225fa6fb860cd0cb4a38b2adce8b4a8560d1cf70f01eb0298742463</x:v>
       </x:c>
       <x:c r="M40" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N40" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="O40" s="11" t="str">
         <x:v>https://df.nexon.com/guide?no=1286</x:v>
@@ -5879,49 +5880,49 @@
     </x:row>
     <x:row r="41" ht="54" customHeight="1">
       <x:c r="A41" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B41" s="11" t="str">
-        <x:v>required_level</x:v>
+        <x:v>equipment_extra_fee</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>인형사 전문직업</x:v>
+        <x:v>장비류 아이템 트레이드</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>required_character_level</x:v>
+        <x:v>additional_fee</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>percentage</x:v>
       </x:c>
       <x:c r="G41" s="11" t="str">
-        <x:v>[20]</x:v>
+        <x:v>[2]</x:v>
       </x:c>
       <x:c r="H41" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I41" s="11" t="str">
-        <x:v>캐릭터 20레벨을 달성하면</x:v>
+        <x:v>장비류 아이템인 경우에는 2%의 수수료가 추가로 부과됩니다.(총 5%)</x:v>
       </x:c>
       <x:c r="J41" s="11" t="str">
-        <x:v>인형사</x:v>
+        <x:v>트레이드</x:v>
       </x:c>
       <x:c r="K41" s="11" t="str">
-        <x:v>document_sha256_053ed5d126b92b3f43c8da673929c088b52ba852356ce0bd2291e606cd642fae</x:v>
+        <x:v>document_sha256_15bd7d49ee6067b02b600bb64ea81bf9e9272b5c70820eb819bcf224cde1942a</x:v>
       </x:c>
       <x:c r="L41" s="11" t="str">
-        <x:v>chunk_sha256_24eca6ca4822155ef952fa759e98dcd41c7cc44dc9132c90d0775665315eed40</x:v>
+        <x:v>chunk_sha256_062cf0c88225fa6fb860cd0cb4a38b2adce8b4a8560d1cf70f01eb0298742463</x:v>
       </x:c>
       <x:c r="M41" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="N41" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="O41" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1270</x:v>
+        <x:v>https://df.nexon.com/guide?no=1286</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="54" customHeight="1">
@@ -5929,7 +5930,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B42" s="11" t="str">
-        <x:v>cube_quantity</x:v>
+        <x:v>required_level</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
         <x:v>supported</x:v>
@@ -5938,19 +5939,19 @@
         <x:v>인형사 전문직업</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
-        <x:v>required_colorless_cube_fragments</x:v>
+        <x:v>required_character_level</x:v>
       </x:c>
       <x:c r="F42" s="11" t="str">
         <x:v>number</x:v>
       </x:c>
       <x:c r="G42" s="11" t="str">
-        <x:v>[100]</x:v>
+        <x:v>[20]</x:v>
       </x:c>
       <x:c r="H42" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="11" t="str">
-        <x:v>무색 큐브 조각 100개를 가져가면</x:v>
+        <x:v>캐릭터 20레벨을 달성하면</x:v>
       </x:c>
       <x:c r="J42" s="11" t="str">
         <x:v>인형사</x:v>
@@ -5962,10 +5963,10 @@
         <x:v>chunk_sha256_24eca6ca4822155ef952fa759e98dcd41c7cc44dc9132c90d0775665315eed40</x:v>
       </x:c>
       <x:c r="M42" s="11" t="n">
-        <x:v>145</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="N42" s="11" t="n">
-        <x:v>164</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="O42" s="11" t="str">
         <x:v>https://df.nexon.com/guide?no=1270</x:v>
@@ -5973,49 +5974,49 @@
     </x:row>
     <x:row r="43" ht="54" customHeight="1">
       <x:c r="A43" s="11" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B43" s="11" t="str">
-        <x:v>displayed_information</x:v>
+        <x:v>cube_quantity</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>화면 설명 ②</x:v>
+        <x:v>인형사 전문직업</x:v>
       </x:c>
       <x:c r="E43" s="11" t="str">
-        <x:v>displayed_information</x:v>
+        <x:v>required_colorless_cube_fragments</x:v>
       </x:c>
       <x:c r="F43" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="G43" s="11" t="str">
-        <x:v>["캐릭터에게 적용 중인 효과"]</x:v>
+        <x:v>[100]</x:v>
       </x:c>
       <x:c r="H43" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I43" s="11" t="str">
-        <x:v>| ② | 캐릭터에게 적용되고 있는 효과</x:v>
+        <x:v>무색 큐브 조각 100개를 가져가면</x:v>
       </x:c>
       <x:c r="J43" s="11" t="str">
-        <x:v>화면 설명</x:v>
+        <x:v>인형사</x:v>
       </x:c>
       <x:c r="K43" s="11" t="str">
-        <x:v>document_sha256_12f470e556d6b7e792cdf7233eb51200f3b2259b1972c81e6cca66fb22fb75c0</x:v>
+        <x:v>document_sha256_053ed5d126b92b3f43c8da673929c088b52ba852356ce0bd2291e606cd642fae</x:v>
       </x:c>
       <x:c r="L43" s="11" t="str">
-        <x:v>chunk_sha256_d866e83b7ea12adc742c6909bb466eb0871dcad6a75d7fb31e919aeaa4392d36</x:v>
+        <x:v>chunk_sha256_24eca6ca4822155ef952fa759e98dcd41c7cc44dc9132c90d0775665315eed40</x:v>
       </x:c>
       <x:c r="M43" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="N43" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="O43" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1292</x:v>
+        <x:v>https://df.nexon.com/guide?no=1270</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="54" customHeight="1">
@@ -6023,7 +6024,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B44" s="11" t="str">
-        <x:v>control_keys</x:v>
+        <x:v>displayed_information</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
         <x:v>supported</x:v>
@@ -6032,19 +6033,19 @@
         <x:v>화면 설명 ②</x:v>
       </x:c>
       <x:c r="E44" s="11" t="str">
-        <x:v>control_keys</x:v>
+        <x:v>displayed_information</x:v>
       </x:c>
       <x:c r="F44" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G44" s="11" t="str">
-        <x:v>["키보드 1~6"]</x:v>
+        <x:v>["캐릭터에게 적용 중인 효과"]</x:v>
       </x:c>
       <x:c r="H44" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I44" s="11" t="str">
-        <x:v>키보드 1~6</x:v>
+        <x:v>| ② | 캐릭터에게 적용되고 있는 효과</x:v>
       </x:c>
       <x:c r="J44" s="11" t="str">
         <x:v>화면 설명</x:v>
@@ -6056,10 +6057,10 @@
         <x:v>chunk_sha256_d866e83b7ea12adc742c6909bb466eb0871dcad6a75d7fb31e919aeaa4392d36</x:v>
       </x:c>
       <x:c r="M44" s="11" t="n">
-        <x:v>159</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="N44" s="11" t="n">
-        <x:v>166</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="O44" s="11" t="str">
         <x:v>https://df.nexon.com/guide?no=1292</x:v>
@@ -6067,96 +6068,96 @@
     </x:row>
     <x:row r="45" ht="54" customHeight="1">
       <x:c r="A45" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B45" s="11" t="str">
-        <x:v>supported_levels</x:v>
+        <x:v>control_keys</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
-        <x:v>장비 시뮬레이터</x:v>
+        <x:v>화면 설명 ②</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str">
-        <x:v>supported_equipment_levels</x:v>
+        <x:v>control_keys</x:v>
       </x:c>
       <x:c r="F45" s="11" t="str">
-        <x:v>entity_list</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="G45" s="11" t="str">
-        <x:v>[110,115]</x:v>
+        <x:v>["키보드 1~6"]</x:v>
       </x:c>
       <x:c r="H45" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="11" t="str">
-        <x:v>110레벨 장비 또는 115레벨 장비</x:v>
+        <x:v>키보드 1~6</x:v>
       </x:c>
       <x:c r="J45" s="11" t="str">
-        <x:v>[시스템] 장비 시뮬레이터</x:v>
+        <x:v>화면 설명</x:v>
       </x:c>
       <x:c r="K45" s="11" t="str">
-        <x:v>document_sha256_13859d266b067df0fd3bd0d1306d3f05eb676603aea78af25add514935864db0</x:v>
+        <x:v>document_sha256_12f470e556d6b7e792cdf7233eb51200f3b2259b1972c81e6cca66fb22fb75c0</x:v>
       </x:c>
       <x:c r="L45" s="11" t="str">
-        <x:v>chunk_sha256_13df4db71148e20bbb4b7e34ae563a8c06841d4063dcbf175dc4a81bf6d2472c</x:v>
+        <x:v>chunk_sha256_d866e83b7ea12adc742c6909bb466eb0871dcad6a75d7fb31e919aeaa4392d36</x:v>
       </x:c>
       <x:c r="M45" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="N45" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="O45" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1494</x:v>
+        <x:v>https://df.nexon.com/guide?no=1292</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="54" customHeight="1">
       <x:c r="A46" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B46" s="11" t="str">
-        <x:v>part_count</x:v>
+        <x:v>supported_levels</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D46" s="11" t="str">
-        <x:v>아바타</x:v>
+        <x:v>장비 시뮬레이터</x:v>
       </x:c>
       <x:c r="E46" s="11" t="str">
-        <x:v>part_count</x:v>
+        <x:v>supported_equipment_levels</x:v>
       </x:c>
       <x:c r="F46" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>entity_list</x:v>
       </x:c>
       <x:c r="G46" s="11" t="str">
-        <x:v>[11]</x:v>
+        <x:v>[110,115]</x:v>
       </x:c>
       <x:c r="H46" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I46" s="11" t="str">
-        <x:v>오라, 총 11부위</x:v>
+        <x:v>110레벨 장비 또는 115레벨 장비</x:v>
       </x:c>
       <x:c r="J46" s="11" t="str">
-        <x:v>아바타</x:v>
+        <x:v>[시스템] 장비 시뮬레이터</x:v>
       </x:c>
       <x:c r="K46" s="11" t="str">
-        <x:v>document_sha256_1625601cede341b4c5ef6235709498e386314876a9722893b369a703c3d73afc</x:v>
+        <x:v>document_sha256_13859d266b067df0fd3bd0d1306d3f05eb676603aea78af25add514935864db0</x:v>
       </x:c>
       <x:c r="L46" s="11" t="str">
-        <x:v>chunk_sha256_bcf28abc5dd98b5cf51d320250feced852e990d1eacf3cfaeb5e59e32eca5780</x:v>
+        <x:v>chunk_sha256_13df4db71148e20bbb4b7e34ae563a8c06841d4063dcbf175dc4a81bf6d2472c</x:v>
       </x:c>
       <x:c r="M46" s="11" t="n">
-        <x:v>157</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N46" s="11" t="n">
-        <x:v>167</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O46" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1280</x:v>
+        <x:v>https://df.nexon.com/guide?no=1494</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="54" customHeight="1">
@@ -6164,28 +6165,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B47" s="11" t="str">
-        <x:v>preset_limit</x:v>
+        <x:v>part_count</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>unsupported</x:v>
+        <x:v>supported</x:v>
       </x:c>
       <x:c r="D47" s="11" t="str">
-        <x:v>아바타 프리셋</x:v>
+        <x:v>아바타</x:v>
       </x:c>
       <x:c r="E47" s="11" t="str">
-        <x:v>maximum_saved_presets</x:v>
+        <x:v>part_count</x:v>
       </x:c>
       <x:c r="F47" s="11" t="str">
         <x:v>number</x:v>
       </x:c>
       <x:c r="G47" s="11" t="str">
-        <x:v>[]</x:v>
+        <x:v>[11]</x:v>
       </x:c>
       <x:c r="H47" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I47" s="11" t="str">
-        <x:v>(공식 문서에서 근거 없음)</x:v>
+        <x:v>오라, 총 11부위</x:v>
       </x:c>
       <x:c r="J47" s="11" t="str">
         <x:v>아바타</x:v>
@@ -6193,200 +6194,199 @@
       <x:c r="K47" s="11" t="str">
         <x:v>document_sha256_1625601cede341b4c5ef6235709498e386314876a9722893b369a703c3d73afc</x:v>
       </x:c>
-      <x:c r="L47" s="11"/>
-      <x:c r="M47" s="11"/>
-      <x:c r="N47" s="11"/>
+      <x:c r="L47" s="11" t="str">
+        <x:v>chunk_sha256_bcf28abc5dd98b5cf51d320250feced852e990d1eacf3cfaeb5e59e32eca5780</x:v>
+      </x:c>
+      <x:c r="M47" s="11" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="N47" s="11" t="n">
+        <x:v>167</x:v>
+      </x:c>
       <x:c r="O47" s="11" t="str">
         <x:v>https://df.nexon.com/guide?no=1280</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="54" customHeight="1">
       <x:c r="A48" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B48" s="11" t="str">
-        <x:v>location</x:v>
+        <x:v>preset_limit</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>supported</x:v>
+        <x:v>unsupported</x:v>
       </x:c>
       <x:c r="D48" s="11" t="str">
-        <x:v>스킬별 제압력 수치</x:v>
+        <x:v>아바타 프리셋</x:v>
       </x:c>
       <x:c r="E48" s="11" t="str">
-        <x:v>lookup_location</x:v>
+        <x:v>maximum_saved_presets</x:v>
       </x:c>
       <x:c r="F48" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="G48" s="11" t="str">
-        <x:v>["스킬 정보(툴팁)"]</x:v>
+        <x:v>[]</x:v>
       </x:c>
       <x:c r="H48" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I48" s="11" t="str">
-        <x:v>각 스킬의 제압력 수치는 스킬 정보(툴팁)에서 확인 가능합니다.</x:v>
+        <x:v>(공식 문서에서 근거 없음)</x:v>
       </x:c>
       <x:c r="J48" s="11" t="str">
-        <x:v>[전투] 제압</x:v>
+        <x:v>아바타</x:v>
       </x:c>
       <x:c r="K48" s="11" t="str">
-        <x:v>document_sha256_01e9021ffc3f1842e206c3502c2da70306d8264a3a4ce4cf04edec6044d248bd</x:v>
-      </x:c>
-      <x:c r="L48" s="11" t="str">
-        <x:v>chunk_sha256_f420c121878a83f26ba93fd24eef208b908493a3cfc206d4e4c80622610b615f</x:v>
-      </x:c>
-      <x:c r="M48" s="11" t="n">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="N48" s="11" t="n">
-        <x:v>206</x:v>
-      </x:c>
+        <x:v>document_sha256_1625601cede341b4c5ef6235709498e386314876a9722893b369a703c3d73afc</x:v>
+      </x:c>
+      <x:c r="L48" s="11"/>
+      <x:c r="M48" s="11"/>
+      <x:c r="N48" s="11"/>
       <x:c r="O48" s="11" t="str">
-        <x:v>https://df.nexon.com/guide?no=1526</x:v>
+        <x:v>https://df.nexon.com/guide?no=1280</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="54" customHeight="1">
       <x:c r="A49" s="11" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B49" s="11" t="str">
-        <x:v>withdrawal_period</x:v>
+        <x:v>location</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D49" s="11" t="str">
-        <x:v>세라 아이템 청약철회</x:v>
+        <x:v>스킬별 제압력 수치</x:v>
       </x:c>
       <x:c r="E49" s="11" t="str">
-        <x:v>withdrawal_period_days</x:v>
+        <x:v>lookup_location</x:v>
       </x:c>
       <x:c r="F49" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="G49" s="11" t="str">
-        <x:v>[7]</x:v>
+        <x:v>["스킬 정보(툴팁)"]</x:v>
       </x:c>
       <x:c r="H49" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I49" s="11" t="str">
-        <x:v>세라로 아이템을 구매 후 7일 이내에 구매를 취소할 수 있는 시스템</x:v>
+        <x:v>각 스킬의 제압력 수치는 스킬 정보(툴팁)에서 확인 가능합니다.</x:v>
       </x:c>
       <x:c r="J49" s="11" t="str">
-        <x:v>[세라 아이템 청약철회] 청약철회란 무엇인가요.</x:v>
+        <x:v>[전투] 제압</x:v>
       </x:c>
       <x:c r="K49" s="11" t="str">
-        <x:v>document_sha256_149d2ff711617b2d1b21a466c228cd8da7080fe6621fb0e3c216bd1141084058</x:v>
+        <x:v>document_sha256_01e9021ffc3f1842e206c3502c2da70306d8264a3a4ce4cf04edec6044d248bd</x:v>
       </x:c>
       <x:c r="L49" s="11" t="str">
-        <x:v>chunk_sha256_74e2e422c2d97239b3a7d5216097c6ff779f6590481ec7f0fba1607907781bbb</x:v>
+        <x:v>chunk_sha256_f420c121878a83f26ba93fd24eef208b908493a3cfc206d4e4c80622610b615f</x:v>
       </x:c>
       <x:c r="M49" s="11" t="n">
-        <x:v>27</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="N49" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="O49" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/faq?faq_no=4950</x:v>
+        <x:v>https://df.nexon.com/guide?no=1526</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="54" customHeight="1">
       <x:c r="A50" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B50" s="11" t="str">
-        <x:v>otp_after_suspension</x:v>
+        <x:v>withdrawal_period</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D50" s="11" t="str">
-        <x:v>모바일 OTP</x:v>
+        <x:v>세라 아이템 청약철회</x:v>
       </x:c>
       <x:c r="E50" s="11" t="str">
-        <x:v>usable_after_phone_suspension</x:v>
+        <x:v>withdrawal_period_days</x:v>
       </x:c>
       <x:c r="F50" s="11" t="str">
-        <x:v>boolean</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="G50" s="11" t="str">
-        <x:v>[true]</x:v>
+        <x:v>[7]</x:v>
       </x:c>
       <x:c r="H50" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I50" s="11" t="str">
-        <x:v>정지된 이후에도 OTP 이용이 가능합니다.</x:v>
+        <x:v>세라로 아이템을 구매 후 7일 이내에 구매를 취소할 수 있는 시스템</x:v>
       </x:c>
       <x:c r="J50" s="11" t="str">
-        <x:v>[네오플OTP] 휴대폰이 정지되면 OTP를 사용할 수 없나요?</x:v>
+        <x:v>[세라 아이템 청약철회] 청약철회란 무엇인가요.</x:v>
       </x:c>
       <x:c r="K50" s="11" t="str">
-        <x:v>document_sha256_14abfdb2580523ff2427fb38999c83b926eb2c0dd50e37367962fe2f76903847</x:v>
+        <x:v>document_sha256_149d2ff711617b2d1b21a466c228cd8da7080fe6621fb0e3c216bd1141084058</x:v>
       </x:c>
       <x:c r="L50" s="11" t="str">
-        <x:v>chunk_sha256_f8419aed79598bff89d650d9f79c25c594ea665e54bf611e33addd1026946280</x:v>
+        <x:v>chunk_sha256_74e2e422c2d97239b3a7d5216097c6ff779f6590481ec7f0fba1607907781bbb</x:v>
       </x:c>
       <x:c r="M50" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="N50" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="O50" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/faq?faq_no=4901</x:v>
+        <x:v>https://df.nexon.com/customer/faq?faq_no=4950</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="54" customHeight="1">
       <x:c r="A51" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B51" s="11" t="str">
-        <x:v>same_account_trade_type</x:v>
+        <x:v>otp_after_suspension</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D51" s="11" t="str">
-        <x:v>히든 레어 아바타 동일 계정 이동</x:v>
+        <x:v>모바일 OTP</x:v>
       </x:c>
       <x:c r="E51" s="11" t="str">
-        <x:v>changes_to_untradeable</x:v>
+        <x:v>usable_after_phone_suspension</x:v>
       </x:c>
       <x:c r="F51" s="11" t="str">
         <x:v>boolean</x:v>
       </x:c>
       <x:c r="G51" s="11" t="str">
-        <x:v>[false]</x:v>
+        <x:v>[true]</x:v>
       </x:c>
       <x:c r="H51" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>동일 계정 내 다른 캐릭터로 우편 이동 시에는
-거래타입이 교환불가 상태로 변경되지 않습니다.</x:v>
+        <x:v>정지된 이후에도 OTP 이용이 가능합니다.</x:v>
       </x:c>
       <x:c r="J51" s="11" t="str">
-        <x:v>[게임 이용] 히든 레어 아바타를 이동시킬 경우 교환이 불가능한가요?</x:v>
+        <x:v>[네오플OTP] 휴대폰이 정지되면 OTP를 사용할 수 없나요?</x:v>
       </x:c>
       <x:c r="K51" s="11" t="str">
-        <x:v>document_sha256_0f18c2d9347d988bec5f4392da02cdd14585f9a53085b978884e22839220188d</x:v>
+        <x:v>document_sha256_14abfdb2580523ff2427fb38999c83b926eb2c0dd50e37367962fe2f76903847</x:v>
       </x:c>
       <x:c r="L51" s="11" t="str">
-        <x:v>chunk_sha256_2073dab6b05ec247292284a0a0a5455a63b1faada4b6ab78a1c64f8dc71b8a22</x:v>
+        <x:v>chunk_sha256_f8419aed79598bff89d650d9f79c25c594ea665e54bf611e33addd1026946280</x:v>
       </x:c>
       <x:c r="M51" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="N51" s="11" t="n">
-        <x:v>165</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="O51" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/faq?faq_no=5001</x:v>
+        <x:v>https://df.nexon.com/customer/faq?faq_no=4901</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="54" customHeight="1">
@@ -6394,13 +6394,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B52" s="11" t="str">
-        <x:v>other_account_trade_type</x:v>
+        <x:v>same_account_trade_type</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D52" s="11" t="str">
-        <x:v>히든 레어 아바타 다른 계정 이동</x:v>
+        <x:v>히든 레어 아바타 동일 계정 이동</x:v>
       </x:c>
       <x:c r="E52" s="11" t="str">
         <x:v>changes_to_untradeable</x:v>
@@ -6409,79 +6409,80 @@
         <x:v>boolean</x:v>
       </x:c>
       <x:c r="G52" s="11" t="str">
+        <x:v>[false]</x:v>
+      </x:c>
+      <x:c r="H52" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I52" s="11" t="str">
+        <x:v>동일 계정 내 다른 캐릭터로 우편 이동 시에는
+거래타입이 교환불가 상태로 변경되지 않습니다.</x:v>
+      </x:c>
+      <x:c r="J52" s="11" t="str">
+        <x:v>[게임 이용] 히든 레어 아바타를 이동시킬 경우 교환이 불가능한가요?</x:v>
+      </x:c>
+      <x:c r="K52" s="11" t="str">
+        <x:v>document_sha256_0f18c2d9347d988bec5f4392da02cdd14585f9a53085b978884e22839220188d</x:v>
+      </x:c>
+      <x:c r="L52" s="11" t="str">
+        <x:v>chunk_sha256_2073dab6b05ec247292284a0a0a5455a63b1faada4b6ab78a1c64f8dc71b8a22</x:v>
+      </x:c>
+      <x:c r="M52" s="11" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N52" s="11" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="O52" s="11" t="str">
+        <x:v>https://df.nexon.com/customer/faq?faq_no=5001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="54" customHeight="1">
+      <x:c r="A53" s="11" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B53" s="11" t="str">
+        <x:v>other_account_trade_type</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="str">
+        <x:v>supported</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="str">
+        <x:v>히든 레어 아바타 다른 계정 이동</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="str">
+        <x:v>changes_to_untradeable</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="G53" s="11" t="str">
         <x:v>[true]</x:v>
       </x:c>
-      <x:c r="H52" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I52" s="11" t="str">
+      <x:c r="H53" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I53" s="11" t="str">
         <x:v>다른 계정으로의 이동(트레이드, 경매장, 아바타마켓 등)이 발생하면
 교환불가 타입으로 변경</x:v>
       </x:c>
-      <x:c r="J52" s="11" t="str">
+      <x:c r="J53" s="11" t="str">
         <x:v>[게임 이용] 히든 레어 아바타를 이동시킬 경우 교환이 불가능한가요?</x:v>
       </x:c>
-      <x:c r="K52" s="11" t="str">
+      <x:c r="K53" s="11" t="str">
         <x:v>document_sha256_0f18c2d9347d988bec5f4392da02cdd14585f9a53085b978884e22839220188d</x:v>
       </x:c>
-      <x:c r="L52" s="11" t="str">
+      <x:c r="L53" s="11" t="str">
         <x:v>chunk_sha256_2073dab6b05ec247292284a0a0a5455a63b1faada4b6ab78a1c64f8dc71b8a22</x:v>
       </x:c>
-      <x:c r="M52" s="11" t="n">
+      <x:c r="M53" s="11" t="n">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="N52" s="11" t="n">
+      <x:c r="N53" s="11" t="n">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="O52" s="11" t="str">
+      <x:c r="O53" s="11" t="str">
         <x:v>https://df.nexon.com/customer/faq?faq_no=5001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="54" customHeight="1">
-      <x:c r="A53" s="11" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B53" s="11" t="str">
-        <x:v>registration_location</x:v>
-      </x:c>
-      <x:c r="C53" s="11" t="str">
-        <x:v>supported</x:v>
-      </x:c>
-      <x:c r="D53" s="11" t="str">
-        <x:v>지정PC</x:v>
-      </x:c>
-      <x:c r="E53" s="11" t="str">
-        <x:v>registration_location</x:v>
-      </x:c>
-      <x:c r="F53" s="11" t="str">
-        <x:v>enum</x:v>
-      </x:c>
-      <x:c r="G53" s="11" t="str">
-        <x:v>["게임 내"]</x:v>
-      </x:c>
-      <x:c r="H53" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I53" s="11" t="str">
-        <x:v>지정PC는 게임 내에서만 등록이 가능</x:v>
-      </x:c>
-      <x:c r="J53" s="11" t="str">
-        <x:v>[지정PC] 지정PC에 대해 궁금한 점이 있어요.</x:v>
-      </x:c>
-      <x:c r="K53" s="11" t="str">
-        <x:v>document_sha256_12bc25ffe3590dcdc5dfcb079470bfd4c702a0655334483e21a7906c2b6ce340</x:v>
-      </x:c>
-      <x:c r="L53" s="11" t="str">
-        <x:v>chunk_sha256_839fa5bc59d9c6ee8d2797c781b6c9e75ba9d204c61d4d3c3a17084a950450af</x:v>
-      </x:c>
-      <x:c r="M53" s="11" t="n">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="N53" s="11" t="n">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="O53" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/faq?faq_no=5630</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="54" customHeight="1">
@@ -6489,7 +6490,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B54" s="11" t="str">
-        <x:v>deletion_location</x:v>
+        <x:v>registration_location</x:v>
       </x:c>
       <x:c r="C54" s="11" t="str">
         <x:v>supported</x:v>
@@ -6498,19 +6499,19 @@
         <x:v>지정PC</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
-        <x:v>deletion_location</x:v>
+        <x:v>registration_location</x:v>
       </x:c>
       <x:c r="F54" s="11" t="str">
-        <x:v>entity_list</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="G54" s="11" t="str">
-        <x:v>["게임","웹"]</x:v>
+        <x:v>["게임 내"]</x:v>
       </x:c>
       <x:c r="H54" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" s="11" t="str">
-        <x:v>삭제는 게임 혹은 웹에서 진행할 수 있습니다.</x:v>
+        <x:v>지정PC는 게임 내에서만 등록이 가능</x:v>
       </x:c>
       <x:c r="J54" s="11" t="str">
         <x:v>[지정PC] 지정PC에 대해 궁금한 점이 있어요.</x:v>
@@ -6522,10 +6523,10 @@
         <x:v>chunk_sha256_839fa5bc59d9c6ee8d2797c781b6c9e75ba9d204c61d4d3c3a17084a950450af</x:v>
       </x:c>
       <x:c r="M54" s="11" t="n">
-        <x:v>231</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="N54" s="11" t="n">
-        <x:v>256</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="O54" s="11" t="str">
         <x:v>https://df.nexon.com/customer/faq?faq_no=5630</x:v>
@@ -6533,49 +6534,49 @@
     </x:row>
     <x:row r="55" ht="54" customHeight="1">
       <x:c r="A55" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B55" s="11" t="str">
-        <x:v>slot_count</x:v>
+        <x:v>deletion_location</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D55" s="11" t="str">
-        <x:v>은 금고</x:v>
+        <x:v>지정PC</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
-        <x:v>slot_count</x:v>
+        <x:v>deletion_location</x:v>
       </x:c>
       <x:c r="F55" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>entity_list</x:v>
       </x:c>
       <x:c r="G55" s="11" t="str">
-        <x:v>[40]</x:v>
+        <x:v>["게임","웹"]</x:v>
       </x:c>
       <x:c r="H55" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" s="11" t="str">
-        <x:v>| 은 금고 | 40 칸 | 400 세라 |</x:v>
+        <x:v>삭제는 게임 혹은 웹에서 진행할 수 있습니다.</x:v>
       </x:c>
       <x:c r="J55" s="11" t="str">
-        <x:v>[게임 이용] 금고 업그레이드 비용 및 단계별 슬롯 수가 궁금해요!</x:v>
+        <x:v>[지정PC] 지정PC에 대해 궁금한 점이 있어요.</x:v>
       </x:c>
       <x:c r="K55" s="11" t="str">
-        <x:v>document_sha256_1134672fc4c263d602529ff36b2f21c8b3231d1c19f104f398f4c48ea6e92b0b</x:v>
+        <x:v>document_sha256_12bc25ffe3590dcdc5dfcb079470bfd4c702a0655334483e21a7906c2b6ce340</x:v>
       </x:c>
       <x:c r="L55" s="11" t="str">
-        <x:v>chunk_sha256_b2f6e4b7973ed004d667c9b752147a6c03726109657d8f309c157cc9312226db</x:v>
+        <x:v>chunk_sha256_839fa5bc59d9c6ee8d2797c781b6c9e75ba9d204c61d4d3c3a17084a950450af</x:v>
       </x:c>
       <x:c r="M55" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="N55" s="11" t="n">
-        <x:v>154</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="O55" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/faq?faq_no=4994</x:v>
+        <x:v>https://df.nexon.com/customer/faq?faq_no=5630</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="54" customHeight="1">
@@ -6583,7 +6584,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>slot_count</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str">
         <x:v>supported</x:v>
@@ -6592,13 +6593,13 @@
         <x:v>은 금고</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>slot_count</x:v>
       </x:c>
       <x:c r="F56" s="11" t="str">
-        <x:v>currency</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="G56" s="11" t="str">
-        <x:v>[{"amount":400,"unit":"세라"}]</x:v>
+        <x:v>[40]</x:v>
       </x:c>
       <x:c r="H56" s="11" t="n">
         <x:v>1</x:v>
@@ -6627,49 +6628,49 @@
     </x:row>
     <x:row r="57" ht="54" customHeight="1">
       <x:c r="A57" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B57" s="11" t="str">
-        <x:v>new_issue_stopped_at</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D57" s="11" t="str">
-        <x:v>고블린패드 신규 발급</x:v>
+        <x:v>은 금고</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
-        <x:v>stopped_at</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="F57" s="11" t="str">
-        <x:v>date</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G57" s="11" t="str">
-        <x:v>["2020-06-25"]</x:v>
+        <x:v>[{"amount":400,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H57" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I57" s="11" t="str">
-        <x:v>2020년 6월 25일 부로 중단되었습니다.</x:v>
+        <x:v>| 은 금고 | 40 칸 | 400 세라 |</x:v>
       </x:c>
       <x:c r="J57" s="11" t="str">
-        <x:v>[고블린패드] 고블린패드 신규 가입이 불가능한가요?</x:v>
+        <x:v>[게임 이용] 금고 업그레이드 비용 및 단계별 슬롯 수가 궁금해요!</x:v>
       </x:c>
       <x:c r="K57" s="11" t="str">
-        <x:v>document_sha256_0e2e3708a583908218fceddd24deac9ec99ed336ffe2f48ffd34b5b0203b50ef</x:v>
+        <x:v>document_sha256_1134672fc4c263d602529ff36b2f21c8b3231d1c19f104f398f4c48ea6e92b0b</x:v>
       </x:c>
       <x:c r="L57" s="11" t="str">
-        <x:v>chunk_sha256_611d6ec7b679543c445c77c70c5ed92310845f2e236c60044afc3180d47601ce</x:v>
+        <x:v>chunk_sha256_b2f6e4b7973ed004d667c9b752147a6c03726109657d8f309c157cc9312226db</x:v>
       </x:c>
       <x:c r="M57" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="N57" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="O57" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/faq?faq_no=4923</x:v>
+        <x:v>https://df.nexon.com/customer/faq?faq_no=4994</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="54" customHeight="1">
@@ -6677,28 +6678,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
-        <x:v>reissue_existing_user</x:v>
+        <x:v>new_issue_stopped_at</x:v>
       </x:c>
       <x:c r="C58" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D58" s="11" t="str">
-        <x:v>고블린패드 기존 이용자</x:v>
+        <x:v>고블린패드 신규 발급</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
-        <x:v>can_reissue</x:v>
+        <x:v>stopped_at</x:v>
       </x:c>
       <x:c r="F58" s="11" t="str">
-        <x:v>boolean</x:v>
+        <x:v>date</x:v>
       </x:c>
       <x:c r="G58" s="11" t="str">
-        <x:v>[true]</x:v>
+        <x:v>["2020-06-25"]</x:v>
       </x:c>
       <x:c r="H58" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I58" s="11" t="str">
-        <x:v>기존 이용 중이신 경우 비밀번호 변경, 재발급이 가능합니다.</x:v>
+        <x:v>2020년 6월 25일 부로 중단되었습니다.</x:v>
       </x:c>
       <x:c r="J58" s="11" t="str">
         <x:v>[고블린패드] 고블린패드 신규 가입이 불가능한가요?</x:v>
@@ -6710,10 +6711,10 @@
         <x:v>chunk_sha256_611d6ec7b679543c445c77c70c5ed92310845f2e236c60044afc3180d47601ce</x:v>
       </x:c>
       <x:c r="M58" s="11" t="n">
-        <x:v>172</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N58" s="11" t="n">
-        <x:v>205</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="O58" s="11" t="str">
         <x:v>https://df.nexon.com/customer/faq?faq_no=4923</x:v>
@@ -6721,49 +6722,49 @@
     </x:row>
     <x:row r="59" ht="54" customHeight="1">
       <x:c r="A59" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B59" s="11" t="str">
-        <x:v>credit_timing</x:v>
+        <x:v>reissue_existing_user</x:v>
       </x:c>
       <x:c r="C59" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D59" s="11" t="str">
-        <x:v>네이버 로그인 계정 이벤트 혜택 1·2 Npay 포인트</x:v>
+        <x:v>고블린패드 기존 이용자</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
-        <x:v>credited_after</x:v>
+        <x:v>can_reissue</x:v>
       </x:c>
       <x:c r="F59" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>boolean</x:v>
       </x:c>
       <x:c r="G59" s="11" t="str">
-        <x:v>[7]</x:v>
+        <x:v>[true]</x:v>
       </x:c>
       <x:c r="H59" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I59" s="11" t="str">
-        <x:v>결제완료 시점으로부터 7일 이후에 적립</x:v>
+        <x:v>기존 이용 중이신 경우 비밀번호 변경, 재발급이 가능합니다.</x:v>
       </x:c>
       <x:c r="J59" s="11" t="str">
-        <x:v>[네이버 로그인 계정 이벤트] [혜택 1,2] 계정 변경 후 Npay 결제를 진행했는데 포인트가 들어오지 않아요.</x:v>
+        <x:v>[고블린패드] 고블린패드 신규 가입이 불가능한가요?</x:v>
       </x:c>
       <x:c r="K59" s="11" t="str">
-        <x:v>document_sha256_15028f170fd1a2268ffc0de2c75cb3c3e821911a1dd2ee1a9cb614e39b4d2172</x:v>
+        <x:v>document_sha256_0e2e3708a583908218fceddd24deac9ec99ed336ffe2f48ffd34b5b0203b50ef</x:v>
       </x:c>
       <x:c r="L59" s="11" t="str">
-        <x:v>chunk_sha256_0fe0865cd60c5a50b0e7df7c2fe7158b671b07cea7e5bd0971748a41e20c7bdc</x:v>
+        <x:v>chunk_sha256_611d6ec7b679543c445c77c70c5ed92310845f2e236c60044afc3180d47601ce</x:v>
       </x:c>
       <x:c r="M59" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="N59" s="11" t="n">
-        <x:v>113</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="O59" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/faq?faq_no=5951</x:v>
+        <x:v>https://df.nexon.com/customer/faq?faq_no=4923</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="54" customHeight="1">
@@ -6771,28 +6772,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="11" t="str">
-        <x:v>credit_amount</x:v>
+        <x:v>credit_timing</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>unsupported</x:v>
+        <x:v>supported</x:v>
       </x:c>
       <x:c r="D60" s="11" t="str">
         <x:v>네이버 로그인 계정 이벤트 혜택 1·2 Npay 포인트</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
-        <x:v>credit_amount</x:v>
+        <x:v>credited_after</x:v>
       </x:c>
       <x:c r="F60" s="11" t="str">
         <x:v>number</x:v>
       </x:c>
       <x:c r="G60" s="11" t="str">
-        <x:v>[]</x:v>
+        <x:v>[7]</x:v>
       </x:c>
       <x:c r="H60" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I60" s="11" t="str">
-        <x:v>(공식 문서에서 근거 없음)</x:v>
+        <x:v>결제완료 시점으로부터 7일 이후에 적립</x:v>
       </x:c>
       <x:c r="J60" s="11" t="str">
         <x:v>[네이버 로그인 계정 이벤트] [혜택 1,2] 계정 변경 후 Npay 결제를 진행했는데 포인트가 들어오지 않아요.</x:v>
@@ -6800,135 +6801,135 @@
       <x:c r="K60" s="11" t="str">
         <x:v>document_sha256_15028f170fd1a2268ffc0de2c75cb3c3e821911a1dd2ee1a9cb614e39b4d2172</x:v>
       </x:c>
-      <x:c r="L60" s="11"/>
-      <x:c r="M60" s="11"/>
-      <x:c r="N60" s="11"/>
+      <x:c r="L60" s="11" t="str">
+        <x:v>chunk_sha256_0fe0865cd60c5a50b0e7df7c2fe7158b671b07cea7e5bd0971748a41e20c7bdc</x:v>
+      </x:c>
+      <x:c r="M60" s="11" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="N60" s="11" t="n">
+        <x:v>113</x:v>
+      </x:c>
       <x:c r="O60" s="11" t="str">
         <x:v>https://df.nexon.com/customer/faq?faq_no=5951</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="54" customHeight="1">
       <x:c r="A61" s="11" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B61" s="11" t="str">
+        <x:v>credit_amount</x:v>
+      </x:c>
+      <x:c r="C61" s="11" t="str">
+        <x:v>unsupported</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="str">
+        <x:v>네이버 로그인 계정 이벤트 혜택 1·2 Npay 포인트</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="str">
+        <x:v>credit_amount</x:v>
+      </x:c>
+      <x:c r="F61" s="11" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="G61" s="11" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="H61" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I61" s="11" t="str">
+        <x:v>(공식 문서에서 근거 없음)</x:v>
+      </x:c>
+      <x:c r="J61" s="11" t="str">
+        <x:v>[네이버 로그인 계정 이벤트] [혜택 1,2] 계정 변경 후 Npay 결제를 진행했는데 포인트가 들어오지 않아요.</x:v>
+      </x:c>
+      <x:c r="K61" s="11" t="str">
+        <x:v>document_sha256_15028f170fd1a2268ffc0de2c75cb3c3e821911a1dd2ee1a9cb614e39b4d2172</x:v>
+      </x:c>
+      <x:c r="L61" s="11"/>
+      <x:c r="M61" s="11"/>
+      <x:c r="N61" s="11"/>
+      <x:c r="O61" s="11" t="str">
+        <x:v>https://df.nexon.com/customer/faq?faq_no=5951</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="54" customHeight="1">
+      <x:c r="A62" s="11" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B61" s="11" t="str">
+      <x:c r="B62" s="11" t="str">
         <x:v>redeem_location</x:v>
       </x:c>
-      <x:c r="C61" s="11" t="str">
-        <x:v>supported</x:v>
-      </x:c>
-      <x:c r="D61" s="11" t="str">
+      <x:c r="C62" s="11" t="str">
+        <x:v>supported</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="str">
         <x:v>세라/넥슨 쿠폰</x:v>
       </x:c>
-      <x:c r="E61" s="11" t="str">
+      <x:c r="E62" s="11" t="str">
         <x:v>redeem_location</x:v>
       </x:c>
-      <x:c r="F61" s="11" t="str">
+      <x:c r="F62" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="G61" s="11" t="str">
+      <x:c r="G62" s="11" t="str">
         <x:v>["던전앤파이터 홈페이지"]</x:v>
       </x:c>
-      <x:c r="H61" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I61" s="11" t="str">
+      <x:c r="H62" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I62" s="11" t="str">
         <x:v>세라/넥슨 쿠폰을 이용하시길 원하신다면
 던파ON이 아닌, 던전앤파이터 홈페이지를 이용해주세요.</x:v>
       </x:c>
-      <x:c r="J61" s="11" t="str">
+      <x:c r="J62" s="11" t="str">
         <x:v>[이용 문의] 이벤트로 받은 세라 쿠폰이 입력되지 않아요.</x:v>
       </x:c>
-      <x:c r="K61" s="11" t="str">
+      <x:c r="K62" s="11" t="str">
         <x:v>document_sha256_0c6454727eb4b218ba26bc6586e062f13d0c5be75e8c062c190f149f22357028</x:v>
       </x:c>
-      <x:c r="L61" s="11" t="str">
+      <x:c r="L62" s="11" t="str">
         <x:v>chunk_sha256_5927e937cb18a4ac2b79b1cbe8a9b5dc05eadf7efc18d9d0efab501cb37832dd</x:v>
       </x:c>
-      <x:c r="M61" s="11" t="n">
+      <x:c r="M62" s="11" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="N61" s="11" t="n">
+      <x:c r="N62" s="11" t="n">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="O61" s="11" t="str">
+      <x:c r="O62" s="11" t="str">
         <x:v>https://df.nexon.com/customer/faq?faq_no=2785</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="54" customHeight="1">
-      <x:c r="A62" s="11" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B62" s="11" t="str">
-        <x:v>effective_date</x:v>
-      </x:c>
-      <x:c r="C62" s="11" t="str">
-        <x:v>supported</x:v>
-      </x:c>
-      <x:c r="D62" s="11" t="str">
-        <x:v>던전앤파이터 운영정책</x:v>
-      </x:c>
-      <x:c r="E62" s="11" t="str">
-        <x:v>effective_at</x:v>
-      </x:c>
-      <x:c r="F62" s="11" t="str">
-        <x:v>date</x:v>
-      </x:c>
-      <x:c r="G62" s="11" t="str">
-        <x:v>["2026-03-15"]</x:v>
-      </x:c>
-      <x:c r="H62" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I62" s="11" t="str">
-        <x:v>본 운영정책은 2026년 3월 15일부터 시행합니다.</x:v>
-      </x:c>
-      <x:c r="J62" s="11" t="str">
-        <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
-      </x:c>
-      <x:c r="K62" s="11" t="str">
-        <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
-      </x:c>
-      <x:c r="L62" s="11" t="str">
-        <x:v>chunk_sha256_57964a47e57ded37dd4b774a35a3cba0bf1819b1002df7a2741c2867477a4110</x:v>
-      </x:c>
-      <x:c r="M62" s="11" t="n">
-        <x:v>1365</x:v>
-      </x:c>
-      <x:c r="N62" s="11" t="n">
-        <x:v>1394</x:v>
-      </x:c>
-      <x:c r="O62" s="11" t="str">
-        <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="54" customHeight="1">
       <x:c r="A63" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B63" s="11" t="str">
-        <x:v>bug_spread_allowed</x:v>
+        <x:v>effective_date</x:v>
       </x:c>
       <x:c r="C63" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D63" s="11" t="str">
-        <x:v>버그 발견 고객</x:v>
+        <x:v>던전앤파이터 운영정책</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
-        <x:v>may_spread_without_reporting</x:v>
+        <x:v>effective_at</x:v>
       </x:c>
       <x:c r="F63" s="11" t="str">
-        <x:v>boolean</x:v>
+        <x:v>date</x:v>
       </x:c>
       <x:c r="G63" s="11" t="str">
-        <x:v>[false]</x:v>
+        <x:v>["2026-03-15"]</x:v>
       </x:c>
       <x:c r="H63" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" s="11" t="str">
-        <x:v>이 의무를 다하지 않고 버그를 악용하거나 타인에게 전파하는 경우 게임이용에 제한을 받을 수 있습니다.</x:v>
+        <x:v>본 운영정책은 2026년 3월 15일부터 시행합니다.</x:v>
       </x:c>
       <x:c r="J63" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -6937,13 +6938,13 @@
         <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
       </x:c>
       <x:c r="L63" s="11" t="str">
-        <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
+        <x:v>chunk_sha256_57964a47e57ded37dd4b774a35a3cba0bf1819b1002df7a2741c2867477a4110</x:v>
       </x:c>
       <x:c r="M63" s="11" t="n">
-        <x:v>1220</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="N63" s="11" t="n">
-        <x:v>1276</x:v>
+        <x:v>1394</x:v>
       </x:c>
       <x:c r="O63" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -6951,31 +6952,31 @@
     </x:row>
     <x:row r="64" ht="54" customHeight="1">
       <x:c r="A64" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B64" s="11" t="str">
-        <x:v>general_rule</x:v>
+        <x:v>bug_spread_allowed</x:v>
       </x:c>
       <x:c r="C64" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D64" s="11" t="str">
-        <x:v>고객 간 사적 분쟁</x:v>
+        <x:v>버그 발견 고객</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
-        <x:v>company_intervention_rule</x:v>
+        <x:v>may_spread_without_reporting</x:v>
       </x:c>
       <x:c r="F64" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>boolean</x:v>
       </x:c>
       <x:c r="G64" s="11" t="str">
-        <x:v>["개입하지 않는 것을 원칙"]</x:v>
+        <x:v>[false]</x:v>
       </x:c>
       <x:c r="H64" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" s="11" t="str">
-        <x:v>사적인 분쟁에 개입하지 않는 것을 원칙</x:v>
+        <x:v>이 의무를 다하지 않고 버그를 악용하거나 타인에게 전파하는 경우 게임이용에 제한을 받을 수 있습니다.</x:v>
       </x:c>
       <x:c r="J64" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -6987,10 +6988,10 @@
         <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
       </x:c>
       <x:c r="M64" s="11" t="n">
-        <x:v>1480</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="N64" s="11" t="n">
-        <x:v>1501</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="O64" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -7001,7 +7002,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B65" s="11" t="str">
-        <x:v>exception</x:v>
+        <x:v>general_rule</x:v>
       </x:c>
       <x:c r="C65" s="11" t="str">
         <x:v>supported</x:v>
@@ -7010,19 +7011,19 @@
         <x:v>고객 간 사적 분쟁</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
-        <x:v>intervention_exception</x:v>
+        <x:v>company_intervention_rule</x:v>
       </x:c>
       <x:c r="F65" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G65" s="11" t="str">
-        <x:v>["불특정 다수의 고객에게 피해를 주는 경우"]</x:v>
+        <x:v>["개입하지 않는 것을 원칙"]</x:v>
       </x:c>
       <x:c r="H65" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I65" s="11" t="str">
-        <x:v>불특정 다수의 고객에게 피해</x:v>
+        <x:v>사적인 분쟁에 개입하지 않는 것을 원칙</x:v>
       </x:c>
       <x:c r="J65" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7034,10 +7035,10 @@
         <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
       </x:c>
       <x:c r="M65" s="11" t="n">
-        <x:v>1630</x:v>
+        <x:v>1480</x:v>
       </x:c>
       <x:c r="N65" s="11" t="n">
-        <x:v>1645</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="O65" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -7045,31 +7046,31 @@
     </x:row>
     <x:row r="66" ht="54" customHeight="1">
       <x:c r="A66" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
-        <x:v>security_service</x:v>
+        <x:v>exception</x:v>
       </x:c>
       <x:c r="C66" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D66" s="11" t="str">
-        <x:v>고객 ID 보호</x:v>
+        <x:v>고객 간 사적 분쟁</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
-        <x:v>security_service_obligation</x:v>
+        <x:v>intervention_exception</x:v>
       </x:c>
       <x:c r="F66" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G66" s="11" t="str">
-        <x:v>["회사가 제공하는 보안서비스 이용"]</x:v>
+        <x:v>["불특정 다수의 고객에게 피해를 주는 경우"]</x:v>
       </x:c>
       <x:c r="H66" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I66" s="11" t="str">
-        <x:v>고객은 자신의 ID를 보호하기 위해 회사에서 제공하는 보안서비스(OTP 등)에 가입하는 등의 노력을 해야 합니다.</x:v>
+        <x:v>불특정 다수의 고객에게 피해</x:v>
       </x:c>
       <x:c r="J66" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7081,10 +7082,10 @@
         <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
       </x:c>
       <x:c r="M66" s="11" t="n">
-        <x:v>757</x:v>
+        <x:v>1630</x:v>
       </x:c>
       <x:c r="N66" s="11" t="n">
-        <x:v>820</x:v>
+        <x:v>1645</x:v>
       </x:c>
       <x:c r="O66" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -7095,7 +7096,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
-        <x:v>credential_secrecy</x:v>
+        <x:v>security_service</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
         <x:v>supported</x:v>
@@ -7104,19 +7105,19 @@
         <x:v>고객 ID 보호</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
-        <x:v>credential_secrecy_obligation</x:v>
+        <x:v>security_service_obligation</x:v>
       </x:c>
       <x:c r="F67" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G67" s="11" t="str">
-        <x:v>["ID와 비밀번호가 타인에게 노출되지 않도록 관리"]</x:v>
+        <x:v>["회사가 제공하는 보안서비스 이용"]</x:v>
       </x:c>
       <x:c r="H67" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I67" s="11" t="str">
-        <x:v>고객은 ID, 비밀번호 등의 계정정보 및 개인정보가 타인에게 노출되지 않도록 최선의 주의를 기울여야 하며</x:v>
+        <x:v>고객은 자신의 ID를 보호하기 위해 회사에서 제공하는 보안서비스(OTP 등)에 가입하는 등의 노력을 해야 합니다.</x:v>
       </x:c>
       <x:c r="J67" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7128,10 +7129,10 @@
         <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
       </x:c>
       <x:c r="M67" s="11" t="n">
-        <x:v>882</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="N67" s="11" t="n">
-        <x:v>940</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="O67" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -7139,31 +7140,31 @@
     </x:row>
     <x:row r="68" ht="54" customHeight="1">
       <x:c r="A68" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
-        <x:v>first_sanction</x:v>
+        <x:v>credential_secrecy</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D68" s="11" t="str">
-        <x:v>운영자/직원 사칭</x:v>
+        <x:v>고객 ID 보호</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
-        <x:v>first_sanction</x:v>
+        <x:v>credential_secrecy_obligation</x:v>
       </x:c>
       <x:c r="F68" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G68" s="11" t="str">
-        <x:v>["100일 게임 이용제한"]</x:v>
+        <x:v>["ID와 비밀번호가 타인에게 노출되지 않도록 관리"]</x:v>
       </x:c>
       <x:c r="H68" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I68" s="11" t="str">
-        <x:v>| 운영자 / 직원을 사칭하는 행위 | 100일 게임 이용제한 | 1년 게임 이용제한 | 3년 게임 이용제한 | 영구 게임 이용제한 |</x:v>
+        <x:v>고객은 ID, 비밀번호 등의 계정정보 및 개인정보가 타인에게 노출되지 않도록 최선의 주의를 기울여야 하며</x:v>
       </x:c>
       <x:c r="J68" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7172,13 +7173,13 @@
         <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
       </x:c>
       <x:c r="L68" s="11" t="str">
-        <x:v>chunk_sha256_794ba7192ebf7b3ed1ed537610afbeb34088b30384ec050fef986ea18357c3a0</x:v>
+        <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
       </x:c>
       <x:c r="M68" s="11" t="n">
-        <x:v>1454</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="N68" s="11" t="n">
-        <x:v>1529</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="O68" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -7189,7 +7190,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B69" s="11" t="str">
-        <x:v>fourth_sanction</x:v>
+        <x:v>first_sanction</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
         <x:v>supported</x:v>
@@ -7198,13 +7199,13 @@
         <x:v>운영자/직원 사칭</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
-        <x:v>fourth_sanction</x:v>
+        <x:v>first_sanction</x:v>
       </x:c>
       <x:c r="F69" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G69" s="11" t="str">
-        <x:v>["영구 게임 이용제한"]</x:v>
+        <x:v>["100일 게임 이용제한"]</x:v>
       </x:c>
       <x:c r="H69" s="11" t="n">
         <x:v>1</x:v>
@@ -7233,31 +7234,31 @@
     </x:row>
     <x:row r="70" ht="54" customHeight="1">
       <x:c r="A70" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B70" s="11" t="str">
-        <x:v>change_notice_method</x:v>
+        <x:v>fourth_sanction</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D70" s="11" t="str">
-        <x:v>던전앤파이터 운영정책 변경</x:v>
+        <x:v>운영자/직원 사칭</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
-        <x:v>notice_method</x:v>
+        <x:v>fourth_sanction</x:v>
       </x:c>
       <x:c r="F70" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G70" s="11" t="str">
-        <x:v>["공지를 통해 안내"]</x:v>
+        <x:v>["영구 게임 이용제한"]</x:v>
       </x:c>
       <x:c r="H70" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I70" s="11" t="str">
-        <x:v>운영정책을 변경할 경우, 회사는 관련 내용을 넥슨 공식 홈페이지(http://www.nexon.com)나 게임 홈페이지(http://df.nexon.com) 공지를 통해 알려드립니다.</x:v>
+        <x:v>| 운영자 / 직원을 사칭하는 행위 | 100일 게임 이용제한 | 1년 게임 이용제한 | 3년 게임 이용제한 | 영구 게임 이용제한 |</x:v>
       </x:c>
       <x:c r="J70" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7266,13 +7267,13 @@
         <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
       </x:c>
       <x:c r="L70" s="11" t="str">
-        <x:v>chunk_sha256_9fef8454ca5da401a3eb86ef4919448898883b1f891861c4670207059eaf3c33</x:v>
+        <x:v>chunk_sha256_794ba7192ebf7b3ed1ed537610afbeb34088b30384ec050fef986ea18357c3a0</x:v>
       </x:c>
       <x:c r="M70" s="11" t="n">
-        <x:v>1084</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="N70" s="11" t="n">
-        <x:v>1186</x:v>
+        <x:v>1529</x:v>
       </x:c>
       <x:c r="O70" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -7280,31 +7281,31 @@
     </x:row>
     <x:row r="71" ht="54" customHeight="1">
       <x:c r="A71" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
-        <x:v>appeal_channel</x:v>
+        <x:v>change_notice_method</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D71" s="11" t="str">
-        <x:v>게임 이용제한 이의신청</x:v>
+        <x:v>던전앤파이터 운영정책 변경</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
-        <x:v>appeal_channel</x:v>
+        <x:v>notice_method</x:v>
       </x:c>
       <x:c r="F71" s="11" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="G71" s="11" t="str">
-        <x:v>["고객센터"]</x:v>
+        <x:v>["공지를 통해 안내"]</x:v>
       </x:c>
       <x:c r="H71" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I71" s="11" t="str">
-        <x:v>이용제한 적용 시 이의신청을 원하실 경우, 고객센터로 문의하여 주시기 바랍니다.</x:v>
+        <x:v>운영정책을 변경할 경우, 회사는 관련 내용을 넥슨 공식 홈페이지(http://www.nexon.com)나 게임 홈페이지(http://df.nexon.com) 공지를 통해 알려드립니다.</x:v>
       </x:c>
       <x:c r="J71" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7313,13 +7314,13 @@
         <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
       </x:c>
       <x:c r="L71" s="11" t="str">
-        <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
+        <x:v>chunk_sha256_9fef8454ca5da401a3eb86ef4919448898883b1f891861c4670207059eaf3c33</x:v>
       </x:c>
       <x:c r="M71" s="11" t="n">
-        <x:v>175</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="N71" s="11" t="n">
-        <x:v>219</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="O71" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
@@ -7330,28 +7331,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B72" s="11" t="str">
-        <x:v>processing_days</x:v>
+        <x:v>appeal_channel</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>unsupported</x:v>
+        <x:v>supported</x:v>
       </x:c>
       <x:c r="D72" s="11" t="str">
         <x:v>게임 이용제한 이의신청</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
-        <x:v>processing_days</x:v>
+        <x:v>appeal_channel</x:v>
       </x:c>
       <x:c r="F72" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="G72" s="11" t="str">
-        <x:v>[]</x:v>
+        <x:v>["고객센터"]</x:v>
       </x:c>
       <x:c r="H72" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I72" s="11" t="str">
-        <x:v>(공식 문서에서 근거 없음)</x:v>
+        <x:v>이용제한 적용 시 이의신청을 원하실 경우, 고객센터로 문의하여 주시기 바랍니다.</x:v>
       </x:c>
       <x:c r="J72" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7359,40 +7360,46 @@
       <x:c r="K72" s="11" t="str">
         <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
       </x:c>
-      <x:c r="L72" s="11"/>
-      <x:c r="M72" s="11"/>
-      <x:c r="N72" s="11"/>
+      <x:c r="L72" s="11" t="str">
+        <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
+      </x:c>
+      <x:c r="M72" s="11" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="N72" s="11" t="n">
+        <x:v>219</x:v>
+      </x:c>
       <x:c r="O72" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="54" customHeight="1">
       <x:c r="A73" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B73" s="11" t="str">
-        <x:v>retention_days</x:v>
+        <x:v>processing_days</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
-        <x:v>supported</x:v>
+        <x:v>unsupported</x:v>
       </x:c>
       <x:c r="D73" s="11" t="str">
-        <x:v>이용제한 근거 데이터</x:v>
+        <x:v>게임 이용제한 이의신청</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
-        <x:v>retention_days</x:v>
+        <x:v>processing_days</x:v>
       </x:c>
       <x:c r="F73" s="11" t="str">
         <x:v>number</x:v>
       </x:c>
       <x:c r="G73" s="11" t="str">
-        <x:v>[90]</x:v>
+        <x:v>[]</x:v>
       </x:c>
       <x:c r="H73" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I73" s="11" t="str">
-        <x:v>이용제한 근거에 대한 데이터는 관계 법령에 근거하여 90일간 보유</x:v>
+        <x:v>(공식 문서에서 근거 없음)</x:v>
       </x:c>
       <x:c r="J73" s="11" t="str">
         <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
@@ -7400,158 +7407,152 @@
       <x:c r="K73" s="11" t="str">
         <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
       </x:c>
-      <x:c r="L73" s="11" t="str">
-        <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
-      </x:c>
-      <x:c r="M73" s="11" t="n">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="N73" s="11" t="n">
-        <x:v>259</x:v>
-      </x:c>
+      <x:c r="L73" s="11"/>
+      <x:c r="M73" s="11"/>
+      <x:c r="N73" s="11"/>
       <x:c r="O73" s="11" t="str">
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="54" customHeight="1">
       <x:c r="A74" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B74" s="11" t="str">
-        <x:v>deletion_at</x:v>
+        <x:v>retention_days</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D74" s="11" t="str">
-        <x:v>[프리미엄 코인샵]트로피컬 바캉스 무기 아바타 상자</x:v>
+        <x:v>이용제한 근거 데이터</x:v>
       </x:c>
       <x:c r="E74" s="11" t="str">
-        <x:v>deletion_at</x:v>
+        <x:v>retention_days</x:v>
       </x:c>
       <x:c r="F74" s="11" t="str">
-        <x:v>datetime</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="G74" s="11" t="str">
-        <x:v>["2026-08-27T06:00:00+09:00"]</x:v>
+        <x:v>[90]</x:v>
       </x:c>
       <x:c r="H74" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I74" s="11" t="str">
-        <x:v>| [프리미엄 코인샵]트로피컬 바캉스 무기 아바타 상자 | 2개 | 계정당 5회 | 2026년 8월 27일 06시 |</x:v>
+        <x:v>이용제한 근거에 대한 데이터는 관계 법령에 근거하여 90일간 보유</x:v>
       </x:c>
       <x:c r="J74" s="11" t="str">
-        <x:v>프리미엄 코인샵</x:v>
+        <x:v>던전앤파이터 운영정책 (2026-03-15 시행)</x:v>
       </x:c>
       <x:c r="K74" s="11" t="str">
-        <x:v>document_sha256_dde0974f824042704eff7e7c8f0fed589a3c70bcd1d43f7dd48f641272cbccdf</x:v>
+        <x:v>document_sha256_c7b4d4825f1bd82bfbad1db55d678070653c9c3b81e7c68c534eb4e698c32ded</x:v>
       </x:c>
       <x:c r="L74" s="11" t="str">
-        <x:v>chunk_sha256_f002c2893434cb114c5a48d9c4b80d195b722d24b0a5a0ad57cbea04b3ab5c7d</x:v>
+        <x:v>chunk_sha256_89cd3ff19da0087bafabc531b84e42e0f9792150cc38c3797cafc3c67317f787</x:v>
       </x:c>
       <x:c r="M74" s="11" t="n">
-        <x:v>328</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="N74" s="11" t="n">
-        <x:v>393</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="O74" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/378</x:v>
+        <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="54" customHeight="1">
       <x:c r="A75" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B75" s="11" t="str">
-        <x:v>applies_to_amplification</x:v>
+        <x:v>deletion_at</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D75" s="11" t="str">
-        <x:v>장비 보호권</x:v>
+        <x:v>[프리미엄 코인샵]트로피컬 바캉스 무기 아바타 상자</x:v>
       </x:c>
       <x:c r="E75" s="11" t="str">
-        <x:v>applies_to_amplification</x:v>
+        <x:v>deletion_at</x:v>
       </x:c>
       <x:c r="F75" s="11" t="str">
-        <x:v>boolean</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="G75" s="11" t="str">
-        <x:v>[false]</x:v>
+        <x:v>["2026-08-27T06:00:00+09:00"]</x:v>
       </x:c>
       <x:c r="H75" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" s="11" t="str">
-        <x:v>| 장비 보호권 | 9,800 세라 | 교환가능 | NPC 키리의 강화 메뉴나 1회용 강화기를 사용해서 무기를 13강 이상 / 그 외 장비를 11강 이상으로 강화에 시도하는 경우, 강화에 실패하여 장비가 파괴될 때 캐릭터 인벤토리에 있는 장비 보호권 1개가 자동으로 소모되면서 장비를 보호합니다. 파괴로부터 보호된 장비는 강화 수치가 +0이 됩니다. 증폭에는 적용 되지 않습니다. | 무제한 | |</x:v>
+        <x:v>| [프리미엄 코인샵]트로피컬 바캉스 무기 아바타 상자 | 2개 | 계정당 5회 | 2026년 8월 27일 06시 |</x:v>
       </x:c>
       <x:c r="J75" s="11" t="str">
-        <x:v>[아이템]장비</x:v>
+        <x:v>프리미엄 코인샵</x:v>
       </x:c>
       <x:c r="K75" s="11" t="str">
-        <x:v>document_sha256_b0daa81f2cf1dd45e310438e756758286acf699da12fbfe67e0104c5d4dc9396</x:v>
+        <x:v>document_sha256_dde0974f824042704eff7e7c8f0fed589a3c70bcd1d43f7dd48f641272cbccdf</x:v>
       </x:c>
       <x:c r="L75" s="11" t="str">
-        <x:v>chunk_sha256_2e9a0d7f09542e4cb1f2cdc72626b889a161141499c5adc06c6bef606d9b5866</x:v>
+        <x:v>chunk_sha256_f002c2893434cb114c5a48d9c4b80d195b722d24b0a5a0ad57cbea04b3ab5c7d</x:v>
       </x:c>
       <x:c r="M75" s="11" t="n">
-        <x:v>432</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="N75" s="11" t="n">
-        <x:v>654</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="O75" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/634</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/378</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="54" customHeight="1">
       <x:c r="A76" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B76" s="11" t="str">
-        <x:v>top_price</x:v>
+        <x:v>applies_to_amplification</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D76" s="11" t="str">
-        <x:v>상의 아바타</x:v>
+        <x:v>장비 보호권</x:v>
       </x:c>
       <x:c r="E76" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>applies_to_amplification</x:v>
       </x:c>
       <x:c r="F76" s="11" t="str">
-        <x:v>currency</x:v>
+        <x:v>boolean</x:v>
       </x:c>
       <x:c r="G76" s="11" t="str">
-        <x:v>[{"amount":6500,"unit":"세라"}]</x:v>
+        <x:v>[false]</x:v>
       </x:c>
       <x:c r="H76" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I76" s="11" t="str">
-        <x:v>| 상의 | 6,500 세라 |</x:v>
+        <x:v>| 장비 보호권 | 9,800 세라 | 교환가능 | NPC 키리의 강화 메뉴나 1회용 강화기를 사용해서 무기를 13강 이상 / 그 외 장비를 11강 이상으로 강화에 시도하는 경우, 강화에 실패하여 장비가 파괴될 때 캐릭터 인벤토리에 있는 장비 보호권 1개가 자동으로 소모되면서 장비를 보호합니다. 파괴로부터 보호된 장비는 강화 수치가 +0이 됩니다. 증폭에는 적용 되지 않습니다. | 무제한 | |</x:v>
       </x:c>
       <x:c r="J76" s="11" t="str">
-        <x:v>[아바타]아바타 관련 안내</x:v>
+        <x:v>[아이템]장비</x:v>
       </x:c>
       <x:c r="K76" s="11" t="str">
-        <x:v>document_sha256_2ea2a1983638bd8aaf07d2d083ebc8dd191d95d40d4e561af31168af00175687</x:v>
+        <x:v>document_sha256_b0daa81f2cf1dd45e310438e756758286acf699da12fbfe67e0104c5d4dc9396</x:v>
       </x:c>
       <x:c r="L76" s="11" t="str">
-        <x:v>chunk_sha256_7b9d2851a009250dd3d8d0c52753cc9530b1ccbd942614e5bcd0fb815dfac5ba</x:v>
+        <x:v>chunk_sha256_2e9a0d7f09542e4cb1f2cdc72626b889a161141499c5adc06c6bef606d9b5866</x:v>
       </x:c>
       <x:c r="M76" s="11" t="n">
-        <x:v>276</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="N76" s="11" t="n">
-        <x:v>293</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="O76" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/647</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/634</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="54" customHeight="1">
@@ -7559,13 +7560,13 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B77" s="11" t="str">
-        <x:v>clone_top_price</x:v>
+        <x:v>top_price</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D77" s="11" t="str">
-        <x:v>상의 클론 아바타</x:v>
+        <x:v>상의 아바타</x:v>
       </x:c>
       <x:c r="E77" s="11" t="str">
         <x:v>price</x:v>
@@ -7574,13 +7575,13 @@
         <x:v>currency</x:v>
       </x:c>
       <x:c r="G77" s="11" t="str">
-        <x:v>[{"amount":2600,"unit":"세라"}]</x:v>
+        <x:v>[{"amount":6500,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H77" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I77" s="11" t="str">
-        <x:v>| 상의 클론 | 2,600 세라 |</x:v>
+        <x:v>| 상의 | 6,500 세라 |</x:v>
       </x:c>
       <x:c r="J77" s="11" t="str">
         <x:v>[아바타]아바타 관련 안내</x:v>
@@ -7589,13 +7590,13 @@
         <x:v>document_sha256_2ea2a1983638bd8aaf07d2d083ebc8dd191d95d40d4e561af31168af00175687</x:v>
       </x:c>
       <x:c r="L77" s="11" t="str">
-        <x:v>chunk_sha256_f7f4b19f8fa40966f97c062f8dcec6e9fa43323c3cf3986703fe43b9474d82e0</x:v>
+        <x:v>chunk_sha256_7b9d2851a009250dd3d8d0c52753cc9530b1ccbd942614e5bcd0fb815dfac5ba</x:v>
       </x:c>
       <x:c r="M77" s="11" t="n">
-        <x:v>1055</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="N77" s="11" t="n">
-        <x:v>1075</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="O77" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/seriashop/647</x:v>
@@ -7603,16 +7604,16 @@
     </x:row>
     <x:row r="78" ht="54" customHeight="1">
       <x:c r="A78" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B78" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>clone_top_price</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D78" s="11" t="str">
-        <x:v>통큰 패키지 A</x:v>
+        <x:v>상의 클론 아바타</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>price</x:v>
@@ -7621,31 +7622,31 @@
         <x:v>currency</x:v>
       </x:c>
       <x:c r="G78" s="11" t="str">
-        <x:v>[{"amount":22600,"unit":"세라"}]</x:v>
+        <x:v>[{"amount":2600,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H78" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I78" s="11" t="str">
-        <x:v>| 통큰 패키지 A | 22,600 세라 | 계정귀속 | 달인의 계약 30일, 패왕의 계약 30일, 가브리엘의 계약 30일, 해방의 열쇠 10개가 들어 있습니다. 가브리엘의 계약 : 가브리엘의 등장확률과 판매종류 및 개수가 증가합니다.(단, 에픽조각교환 가브리엘은 제외) | 무제한 | |</x:v>
+        <x:v>| 상의 클론 | 2,600 세라 |</x:v>
       </x:c>
       <x:c r="J78" s="11" t="str">
-        <x:v>[아이템] 기타</x:v>
+        <x:v>[아바타]아바타 관련 안내</x:v>
       </x:c>
       <x:c r="K78" s="11" t="str">
-        <x:v>document_sha256_378049759f0825db5bf34244015033332f4487db2e41dbde25db1f81bb78a045</x:v>
+        <x:v>document_sha256_2ea2a1983638bd8aaf07d2d083ebc8dd191d95d40d4e561af31168af00175687</x:v>
       </x:c>
       <x:c r="L78" s="11" t="str">
-        <x:v>chunk_sha256_8ed3e3b0a1e1e2ecbc934f274dd8662b55e141689d21297ef64c01a7374abb96</x:v>
+        <x:v>chunk_sha256_f7f4b19f8fa40966f97c062f8dcec6e9fa43323c3cf3986703fe43b9474d82e0</x:v>
       </x:c>
       <x:c r="M78" s="11" t="n">
-        <x:v>225</x:v>
+        <x:v>1055</x:v>
       </x:c>
       <x:c r="N78" s="11" t="n">
-        <x:v>386</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="O78" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/647</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="54" customHeight="1">
@@ -7653,7 +7654,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B79" s="11" t="str">
-        <x:v>trade_type</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
         <x:v>supported</x:v>
@@ -7662,13 +7663,13 @@
         <x:v>통큰 패키지 A</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
-        <x:v>trade_type</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="F79" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G79" s="11" t="str">
-        <x:v>["계정귀속"]</x:v>
+        <x:v>[{"amount":22600,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H79" s="11" t="n">
         <x:v>1</x:v>
@@ -7700,7 +7701,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B80" s="11" t="str">
-        <x:v>duration</x:v>
+        <x:v>trade_type</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
         <x:v>supported</x:v>
@@ -7709,13 +7710,13 @@
         <x:v>통큰 패키지 A</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
-        <x:v>duration</x:v>
+        <x:v>trade_type</x:v>
       </x:c>
       <x:c r="F80" s="11" t="str">
         <x:v>enum</x:v>
       </x:c>
       <x:c r="G80" s="11" t="str">
-        <x:v>["무제한"]</x:v>
+        <x:v>["계정귀속"]</x:v>
       </x:c>
       <x:c r="H80" s="11" t="n">
         <x:v>1</x:v>
@@ -7744,49 +7745,49 @@
     </x:row>
     <x:row r="81" ht="54" customHeight="1">
       <x:c r="A81" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B81" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>duration</x:v>
       </x:c>
       <x:c r="C81" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D81" s="11" t="str">
-        <x:v>증폭 보호권</x:v>
+        <x:v>통큰 패키지 A</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>duration</x:v>
       </x:c>
       <x:c r="F81" s="11" t="str">
-        <x:v>currency</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="G81" s="11" t="str">
-        <x:v>[{"amount":12900,"unit":"세라"}]</x:v>
+        <x:v>["무제한"]</x:v>
       </x:c>
       <x:c r="H81" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I81" s="11" t="str">
-        <x:v>| 증폭 보호권 | 12,900 세라 | 교환가능 |</x:v>
+        <x:v>| 통큰 패키지 A | 22,600 세라 | 계정귀속 | 달인의 계약 30일, 패왕의 계약 30일, 가브리엘의 계약 30일, 해방의 열쇠 10개가 들어 있습니다. 가브리엘의 계약 : 가브리엘의 등장확률과 판매종류 및 개수가 증가합니다.(단, 에픽조각교환 가브리엘은 제외) | 무제한 | |</x:v>
       </x:c>
       <x:c r="J81" s="11" t="str">
-        <x:v>[아이템]장비</x:v>
+        <x:v>[아이템] 기타</x:v>
       </x:c>
       <x:c r="K81" s="11" t="str">
-        <x:v>document_sha256_b0daa81f2cf1dd45e310438e756758286acf699da12fbfe67e0104c5d4dc9396</x:v>
+        <x:v>document_sha256_378049759f0825db5bf34244015033332f4487db2e41dbde25db1f81bb78a045</x:v>
       </x:c>
       <x:c r="L81" s="11" t="str">
-        <x:v>chunk_sha256_2e9a0d7f09542e4cb1f2cdc72626b889a161141499c5adc06c6bef606d9b5866</x:v>
+        <x:v>chunk_sha256_8ed3e3b0a1e1e2ecbc934f274dd8662b55e141689d21297ef64c01a7374abb96</x:v>
       </x:c>
       <x:c r="M81" s="11" t="n">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="N81" s="11" t="n">
-        <x:v>253</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="O81" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/634</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
@@ -7794,7 +7795,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B82" s="11" t="str">
-        <x:v>trade_type</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="C82" s="11" t="str">
         <x:v>supported</x:v>
@@ -7803,13 +7804,13 @@
         <x:v>증폭 보호권</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
-        <x:v>trade_type</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="F82" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G82" s="11" t="str">
-        <x:v>["교환가능"]</x:v>
+        <x:v>[{"amount":12900,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H82" s="11" t="n">
         <x:v>1</x:v>
@@ -7838,96 +7839,96 @@
     </x:row>
     <x:row r="83" ht="54" customHeight="1">
       <x:c r="A83" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B83" s="11" t="str">
-        <x:v>gold_coin_price</x:v>
+        <x:v>trade_type</x:v>
       </x:c>
       <x:c r="C83" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D83" s="11" t="str">
-        <x:v>피부 아바타</x:v>
+        <x:v>증폭 보호권</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
-        <x:v>gold_coin_price</x:v>
+        <x:v>trade_type</x:v>
       </x:c>
       <x:c r="F83" s="11" t="str">
-        <x:v>currency</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="G83" s="11" t="str">
-        <x:v>[{"amount":10,"unit":"골드 코인"}]</x:v>
+        <x:v>["교환가능"]</x:v>
       </x:c>
       <x:c r="H83" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I83" s="11" t="str">
-        <x:v>| 피부 | 10 골드 코인 | 교환불가 |</x:v>
+        <x:v>| 증폭 보호권 | 12,900 세라 | 교환가능 |</x:v>
       </x:c>
       <x:c r="J83" s="11" t="str">
-        <x:v>[아바타]아바타 관련 안내</x:v>
+        <x:v>[아이템]장비</x:v>
       </x:c>
       <x:c r="K83" s="11" t="str">
-        <x:v>document_sha256_2ea2a1983638bd8aaf07d2d083ebc8dd191d95d40d4e561af31168af00175687</x:v>
+        <x:v>document_sha256_b0daa81f2cf1dd45e310438e756758286acf699da12fbfe67e0104c5d4dc9396</x:v>
       </x:c>
       <x:c r="L83" s="11" t="str">
-        <x:v>chunk_sha256_a690de0a5155d8fae91debe323d632a7eab908e4979f8f9382a660bb44449428</x:v>
+        <x:v>chunk_sha256_2e9a0d7f09542e4cb1f2cdc72626b889a161141499c5adc06c6bef606d9b5866</x:v>
       </x:c>
       <x:c r="M83" s="11" t="n">
-        <x:v>475</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="N83" s="11" t="n">
-        <x:v>499</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="O83" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/647</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/634</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="54" customHeight="1">
       <x:c r="A84" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>gold_coin_price</x:v>
       </x:c>
       <x:c r="C84" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D84" s="11" t="str">
-        <x:v>하트비트 메가폰 10개</x:v>
+        <x:v>피부 아바타</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
-        <x:v>price</x:v>
+        <x:v>gold_coin_price</x:v>
       </x:c>
       <x:c r="F84" s="11" t="str">
         <x:v>currency</x:v>
       </x:c>
       <x:c r="G84" s="11" t="str">
-        <x:v>[{"amount":5800,"unit":"세라"}]</x:v>
+        <x:v>[{"amount":10,"unit":"골드 코인"}]</x:v>
       </x:c>
       <x:c r="H84" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I84" s="11" t="str">
-        <x:v>| 하트비트 메가폰 10개 | 5,800 세라 | 교환가능 |</x:v>
+        <x:v>| 피부 | 10 골드 코인 | 교환불가 |</x:v>
       </x:c>
       <x:c r="J84" s="11" t="str">
-        <x:v>[아이템] 기타</x:v>
+        <x:v>[아바타]아바타 관련 안내</x:v>
       </x:c>
       <x:c r="K84" s="11" t="str">
-        <x:v>document_sha256_378049759f0825db5bf34244015033332f4487db2e41dbde25db1f81bb78a045</x:v>
+        <x:v>document_sha256_2ea2a1983638bd8aaf07d2d083ebc8dd191d95d40d4e561af31168af00175687</x:v>
       </x:c>
       <x:c r="L84" s="11" t="str">
-        <x:v>chunk_sha256_020577dbaf08b828fbeeb73f527ab3b60ee7d151c6cb86c78895ed8f6ab613c4</x:v>
+        <x:v>chunk_sha256_a690de0a5155d8fae91debe323d632a7eab908e4979f8f9382a660bb44449428</x:v>
       </x:c>
       <x:c r="M84" s="11" t="n">
-        <x:v>330</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="N84" s="11" t="n">
-        <x:v>364</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="O84" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/647</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="54" customHeight="1">
@@ -7935,28 +7936,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B85" s="11" t="str">
-        <x:v>purchase_limit</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="C85" s="11" t="str">
-        <x:v>unsupported</x:v>
+        <x:v>supported</x:v>
       </x:c>
       <x:c r="D85" s="11" t="str">
         <x:v>하트비트 메가폰 10개</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
-        <x:v>account_purchase_limit</x:v>
+        <x:v>price</x:v>
       </x:c>
       <x:c r="F85" s="11" t="str">
-        <x:v>number</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G85" s="11" t="str">
-        <x:v>[]</x:v>
+        <x:v>[{"amount":5800,"unit":"세라"}]</x:v>
       </x:c>
       <x:c r="H85" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I85" s="11" t="str">
-        <x:v>(공식 문서에서 근거 없음)</x:v>
+        <x:v>| 하트비트 메가폰 10개 | 5,800 세라 | 교환가능 |</x:v>
       </x:c>
       <x:c r="J85" s="11" t="str">
         <x:v>[아이템] 기타</x:v>
@@ -7964,40 +7965,46 @@
       <x:c r="K85" s="11" t="str">
         <x:v>document_sha256_378049759f0825db5bf34244015033332f4487db2e41dbde25db1f81bb78a045</x:v>
       </x:c>
-      <x:c r="L85" s="11"/>
-      <x:c r="M85" s="11"/>
-      <x:c r="N85" s="11"/>
+      <x:c r="L85" s="11" t="str">
+        <x:v>chunk_sha256_020577dbaf08b828fbeeb73f527ab3b60ee7d151c6cb86c78895ed8f6ab613c4</x:v>
+      </x:c>
+      <x:c r="M85" s="11" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="N85" s="11" t="n">
+        <x:v>364</x:v>
+      </x:c>
       <x:c r="O85" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
       <x:c r="A86" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B86" s="11" t="str">
-        <x:v>usable_locations</x:v>
+        <x:v>purchase_limit</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
-        <x:v>supported</x:v>
+        <x:v>unsupported</x:v>
       </x:c>
       <x:c r="D86" s="11" t="str">
-        <x:v>무한 올빼미</x:v>
+        <x:v>하트비트 메가폰 10개</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
-        <x:v>usable_locations</x:v>
+        <x:v>account_purchase_limit</x:v>
       </x:c>
       <x:c r="F86" s="11" t="str">
-        <x:v>entity_list</x:v>
+        <x:v>number</x:v>
       </x:c>
       <x:c r="G86" s="11" t="str">
-        <x:v>["마을","던전"]</x:v>
+        <x:v>[]</x:v>
       </x:c>
       <x:c r="H86" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I86" s="11" t="str">
-        <x:v>마을, 던전에서 사용이 가능합니다.</x:v>
+        <x:v>(공식 문서에서 근거 없음)</x:v>
       </x:c>
       <x:c r="J86" s="11" t="str">
         <x:v>[아이템] 기타</x:v>
@@ -8005,72 +8012,66 @@
       <x:c r="K86" s="11" t="str">
         <x:v>document_sha256_378049759f0825db5bf34244015033332f4487db2e41dbde25db1f81bb78a045</x:v>
       </x:c>
-      <x:c r="L86" s="11" t="str">
-        <x:v>chunk_sha256_8ed3e3b0a1e1e2ecbc934f274dd8662b55e141689d21297ef64c01a7374abb96</x:v>
-      </x:c>
-      <x:c r="M86" s="11" t="n">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="N86" s="11" t="n">
-        <x:v>631</x:v>
-      </x:c>
+      <x:c r="L86" s="11"/>
+      <x:c r="M86" s="11"/>
+      <x:c r="N86" s="11"/>
       <x:c r="O86" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
       <x:c r="A87" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B87" s="11" t="str">
-        <x:v>sale_period</x:v>
+        <x:v>usable_locations</x:v>
       </x:c>
       <x:c r="C87" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D87" s="11" t="str">
-        <x:v>7월 이달의 아이템</x:v>
+        <x:v>무한 올빼미</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
-        <x:v>sale_period</x:v>
+        <x:v>usable_locations</x:v>
       </x:c>
       <x:c r="F87" s="11" t="str">
-        <x:v>date_range</x:v>
+        <x:v>entity_list</x:v>
       </x:c>
       <x:c r="G87" s="11" t="str">
-        <x:v>["2026-06-25","2026-07-30"]</x:v>
+        <x:v>["마을","던전"]</x:v>
       </x:c>
       <x:c r="H87" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I87" s="11" t="str">
-        <x:v>판매기간: 06.25 ~ 07.30</x:v>
+        <x:v>마을, 던전에서 사용이 가능합니다.</x:v>
       </x:c>
       <x:c r="J87" s="11" t="str">
-        <x:v>이달의 아이템</x:v>
+        <x:v>[아이템] 기타</x:v>
       </x:c>
       <x:c r="K87" s="11" t="str">
-        <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
+        <x:v>document_sha256_378049759f0825db5bf34244015033332f4487db2e41dbde25db1f81bb78a045</x:v>
       </x:c>
       <x:c r="L87" s="11" t="str">
-        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
+        <x:v>chunk_sha256_8ed3e3b0a1e1e2ecbc934f274dd8662b55e141689d21297ef64c01a7374abb96</x:v>
       </x:c>
       <x:c r="M87" s="11" t="n">
-        <x:v>119</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="N87" s="11" t="n">
-        <x:v>138</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="O87" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="54" customHeight="1">
       <x:c r="A88" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B88" s="11" t="str">
-        <x:v>tradeable</x:v>
+        <x:v>sale_period</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
         <x:v>supported</x:v>
@@ -8079,68 +8080,68 @@
         <x:v>7월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
+        <x:v>sale_period</x:v>
+      </x:c>
+      <x:c r="F88" s="11" t="str">
+        <x:v>date_range</x:v>
+      </x:c>
+      <x:c r="G88" s="11" t="str">
+        <x:v>["2026-06-25","2026-07-30"]</x:v>
+      </x:c>
+      <x:c r="H88" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I88" s="11" t="str">
+        <x:v>판매기간: 06.25 ~ 07.30</x:v>
+      </x:c>
+      <x:c r="J88" s="11" t="str">
+        <x:v>이달의 아이템</x:v>
+      </x:c>
+      <x:c r="K88" s="11" t="str">
+        <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
+      </x:c>
+      <x:c r="L88" s="11" t="str">
+        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
+      </x:c>
+      <x:c r="M88" s="11" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="N88" s="11" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="O88" s="11" t="str">
+        <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="54" customHeight="1">
+      <x:c r="A89" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B89" s="11" t="str">
+        <x:v>tradeable</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="str">
+        <x:v>supported</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="str">
+        <x:v>7월 이달의 아이템</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="str">
         <x:v>is_tradeable</x:v>
       </x:c>
-      <x:c r="F88" s="11" t="str">
+      <x:c r="F89" s="11" t="str">
         <x:v>boolean</x:v>
       </x:c>
-      <x:c r="G88" s="11" t="str">
+      <x:c r="G89" s="11" t="str">
         <x:v>[true]</x:v>
       </x:c>
-      <x:c r="H88" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I88" s="11" t="str">
+      <x:c r="H89" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I89" s="11" t="str">
         <x:v>거래타입
 교환가능</x:v>
       </x:c>
-      <x:c r="J88" s="11" t="str">
-        <x:v>이달의 아이템</x:v>
-      </x:c>
-      <x:c r="K88" s="11" t="str">
-        <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
-      </x:c>
-      <x:c r="L88" s="11" t="str">
-        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
-      </x:c>
-      <x:c r="M88" s="11" t="n">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="N88" s="11" t="n">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="O88" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="54" customHeight="1">
-      <x:c r="A89" s="11" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B89" s="11" t="str">
-        <x:v>obtained_items</x:v>
-      </x:c>
-      <x:c r="C89" s="11" t="str">
-        <x:v>supported</x:v>
-      </x:c>
-      <x:c r="D89" s="11" t="str">
-        <x:v>7월 이달의 아이템</x:v>
-      </x:c>
-      <x:c r="E89" s="11" t="str">
-        <x:v>obtained_items</x:v>
-      </x:c>
-      <x:c r="F89" s="11" t="str">
-        <x:v>entity_list</x:v>
-      </x:c>
-      <x:c r="G89" s="11" t="str">
-        <x:v>["[7월]클론 레어 아바타(교환불가) 풀세트 상자","[7월]찬란한 엠블렘(계정귀속) 풀세트 선택상자"]</x:v>
-      </x:c>
-      <x:c r="H89" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I89" s="11" t="str">
-        <x:v>[7월]클론 레어 아바타(교환불가) 풀세트 상자</x:v>
-      </x:c>
       <x:c r="J89" s="11" t="str">
         <x:v>이달의 아이템</x:v>
       </x:c>
@@ -8151,10 +8152,10 @@
         <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
       </x:c>
       <x:c r="M89" s="11" t="n">
-        <x:v>174</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="N89" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="O89" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
@@ -8183,10 +8184,10 @@
         <x:v>["[7월]클론 레어 아바타(교환불가) 풀세트 상자","[7월]찬란한 엠블렘(계정귀속) 풀세트 선택상자"]</x:v>
       </x:c>
       <x:c r="H90" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I90" s="11" t="str">
-        <x:v>[7월]찬란한 엠블렘(계정귀속) 풀세트 선택상자</x:v>
+        <x:v>[7월]클론 레어 아바타(교환불가) 풀세트 상자</x:v>
       </x:c>
       <x:c r="J90" s="11" t="str">
         <x:v>이달의 아이템</x:v>
@@ -8198,10 +8199,10 @@
         <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
       </x:c>
       <x:c r="M90" s="11" t="n">
-        <x:v>202</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="N90" s="11" t="n">
-        <x:v>228</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="O90" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
@@ -8209,10 +8210,10 @@
     </x:row>
     <x:row r="91" ht="54" customHeight="1">
       <x:c r="A91" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>shop_price</x:v>
+        <x:v>obtained_items</x:v>
       </x:c>
       <x:c r="C91" s="11" t="str">
         <x:v>supported</x:v>
@@ -8221,20 +8222,19 @@
         <x:v>7월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
-        <x:v>shop_price</x:v>
+        <x:v>obtained_items</x:v>
       </x:c>
       <x:c r="F91" s="11" t="str">
-        <x:v>currency</x:v>
+        <x:v>entity_list</x:v>
       </x:c>
       <x:c r="G91" s="11" t="str">
-        <x:v>[{"amount":40000000,"unit":"골드"}]</x:v>
+        <x:v>["[7월]클론 레어 아바타(교환불가) 풀세트 상자","[7월]찬란한 엠블렘(계정귀속) 풀세트 선택상자"]</x:v>
       </x:c>
       <x:c r="H91" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I91" s="11" t="str">
-        <x:v>상점판매가
-4,000만 골드</x:v>
+        <x:v>[7월]찬란한 엠블렘(계정귀속) 풀세트 선택상자</x:v>
       </x:c>
       <x:c r="J91" s="11" t="str">
         <x:v>이달의 아이템</x:v>
@@ -8246,10 +8246,10 @@
         <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
       </x:c>
       <x:c r="M91" s="11" t="n">
-        <x:v>242</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="N91" s="11" t="n">
-        <x:v>257</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="O91" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
@@ -8260,7 +8260,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>deletion_at</x:v>
+        <x:v>shop_price</x:v>
       </x:c>
       <x:c r="C92" s="11" t="str">
         <x:v>supported</x:v>
@@ -8269,19 +8269,20 @@
         <x:v>7월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
-        <x:v>deletion_at</x:v>
+        <x:v>shop_price</x:v>
       </x:c>
       <x:c r="F92" s="11" t="str">
-        <x:v>datetime</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G92" s="11" t="str">
-        <x:v>["2026-08-13T06:00:00+09:00"]</x:v>
+        <x:v>[{"amount":40000000,"unit":"골드"}]</x:v>
       </x:c>
       <x:c r="H92" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I92" s="11" t="str">
-        <x:v>2026년 08월 13일 06시 일괄삭제</x:v>
+        <x:v>상점판매가
+4,000만 골드</x:v>
       </x:c>
       <x:c r="J92" s="11" t="str">
         <x:v>이달의 아이템</x:v>
@@ -8293,10 +8294,10 @@
         <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
       </x:c>
       <x:c r="M92" s="11" t="n">
-        <x:v>273</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="N92" s="11" t="n">
-        <x:v>295</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="O92" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
@@ -8304,10 +8305,10 @@
     </x:row>
     <x:row r="93" ht="54" customHeight="1">
       <x:c r="A93" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B93" s="11" t="str">
-        <x:v>trade_type</x:v>
+        <x:v>deletion_at</x:v>
       </x:c>
       <x:c r="C93" s="11" t="str">
         <x:v>supported</x:v>
@@ -8316,20 +8317,19 @@
         <x:v>7월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
-        <x:v>trade_type</x:v>
+        <x:v>deletion_at</x:v>
       </x:c>
       <x:c r="F93" s="11" t="str">
-        <x:v>enum</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="G93" s="11" t="str">
-        <x:v>["교환가능"]</x:v>
+        <x:v>["2026-08-13T06:00:00+09:00"]</x:v>
       </x:c>
       <x:c r="H93" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I93" s="11" t="str">
-        <x:v>거래타입
-교환가능</x:v>
+        <x:v>2026년 08월 13일 06시 일괄삭제</x:v>
       </x:c>
       <x:c r="J93" s="11" t="str">
         <x:v>이달의 아이템</x:v>
@@ -8341,10 +8341,10 @@
         <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
       </x:c>
       <x:c r="M93" s="11" t="n">
-        <x:v>258</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="N93" s="11" t="n">
-        <x:v>267</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="O93" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
@@ -8355,7 +8355,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B94" s="11" t="str">
-        <x:v>shop_price</x:v>
+        <x:v>trade_type</x:v>
       </x:c>
       <x:c r="C94" s="11" t="str">
         <x:v>supported</x:v>
@@ -8364,133 +8364,133 @@
         <x:v>7월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E94" s="11" t="str">
+        <x:v>trade_type</x:v>
+      </x:c>
+      <x:c r="F94" s="11" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="G94" s="11" t="str">
+        <x:v>["교환가능"]</x:v>
+      </x:c>
+      <x:c r="H94" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I94" s="11" t="str">
+        <x:v>거래타입
+교환가능</x:v>
+      </x:c>
+      <x:c r="J94" s="11" t="str">
+        <x:v>이달의 아이템</x:v>
+      </x:c>
+      <x:c r="K94" s="11" t="str">
+        <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
+      </x:c>
+      <x:c r="L94" s="11" t="str">
+        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
+      </x:c>
+      <x:c r="M94" s="11" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="N94" s="11" t="n">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="O94" s="11" t="str">
+        <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="54" customHeight="1">
+      <x:c r="A95" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B95" s="11" t="str">
         <x:v>shop_price</x:v>
       </x:c>
-      <x:c r="F94" s="11" t="str">
+      <x:c r="C95" s="11" t="str">
+        <x:v>supported</x:v>
+      </x:c>
+      <x:c r="D95" s="11" t="str">
+        <x:v>7월 이달의 아이템</x:v>
+      </x:c>
+      <x:c r="E95" s="11" t="str">
+        <x:v>shop_price</x:v>
+      </x:c>
+      <x:c r="F95" s="11" t="str">
         <x:v>currency</x:v>
       </x:c>
-      <x:c r="G94" s="11" t="str">
+      <x:c r="G95" s="11" t="str">
         <x:v>[{"amount":40000000,"unit":"골드"}]</x:v>
       </x:c>
-      <x:c r="H94" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I94" s="11" t="str">
+      <x:c r="H95" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I95" s="11" t="str">
         <x:v>상점판매가
 4,000만 골드</x:v>
       </x:c>
-      <x:c r="J94" s="11" t="str">
+      <x:c r="J95" s="11" t="str">
         <x:v>이달의 아이템</x:v>
       </x:c>
-      <x:c r="K94" s="11" t="str">
+      <x:c r="K95" s="11" t="str">
         <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
       </x:c>
-      <x:c r="L94" s="11" t="str">
+      <x:c r="L95" s="11" t="str">
         <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
       </x:c>
-      <x:c r="M94" s="11" t="n">
+      <x:c r="M95" s="11" t="n">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="N94" s="11" t="n">
+      <x:c r="N95" s="11" t="n">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="O94" s="11" t="str">
+      <x:c r="O95" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="54" customHeight="1">
-      <x:c r="A95" s="11" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B95" s="11" t="str">
-        <x:v>deletion_at</x:v>
-      </x:c>
-      <x:c r="C95" s="11" t="str">
-        <x:v>supported</x:v>
-      </x:c>
-      <x:c r="D95" s="11" t="str">
-        <x:v>6월 이달의 아이템</x:v>
-      </x:c>
-      <x:c r="E95" s="11" t="str">
-        <x:v>deletion_at</x:v>
-      </x:c>
-      <x:c r="F95" s="11" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="G95" s="11" t="str">
-        <x:v>["2026-07-09T06:00:00+09:00"]</x:v>
-      </x:c>
-      <x:c r="H95" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I95" s="11" t="str">
-        <x:v>2026년 7월 9일 06시 일괄삭제</x:v>
-      </x:c>
-      <x:c r="J95" s="11" t="str">
-        <x:v>6월 이달 의 아이템</x:v>
-      </x:c>
-      <x:c r="K95" s="11" t="str">
-        <x:v>document_sha256_8d15942b7c803029b811a23910302f2274bd00a85d68f3c8be8d1a6510122be6</x:v>
-      </x:c>
-      <x:c r="L95" s="11" t="str">
-        <x:v>chunk_sha256_6ca94020f0661c022cf19032640d142d7c07b4e1c0a29f21bc9bf908059ba95b</x:v>
-      </x:c>
-      <x:c r="M95" s="11" t="n">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="N95" s="11" t="n">
-        <x:v>547</x:v>
-      </x:c>
-      <x:c r="O95" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/seriashop/622</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="54" customHeight="1">
       <x:c r="A96" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B96" s="11" t="str">
-        <x:v>july_shop_price</x:v>
+        <x:v>deletion_at</x:v>
       </x:c>
       <x:c r="C96" s="11" t="str">
         <x:v>supported</x:v>
       </x:c>
       <x:c r="D96" s="11" t="str">
-        <x:v>7월 이달의 아이템</x:v>
+        <x:v>6월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E96" s="11" t="str">
-        <x:v>shop_price</x:v>
+        <x:v>deletion_at</x:v>
       </x:c>
       <x:c r="F96" s="11" t="str">
-        <x:v>currency</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="G96" s="11" t="str">
-        <x:v>[{"amount":40000000,"unit":"골드"}]</x:v>
+        <x:v>["2026-07-09T06:00:00+09:00"]</x:v>
       </x:c>
       <x:c r="H96" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I96" s="11" t="str">
-        <x:v>상점판매가
-4,000만 골드</x:v>
+        <x:v>2026년 7월 9일 06시 일괄삭제</x:v>
       </x:c>
       <x:c r="J96" s="11" t="str">
-        <x:v>이달의 아이템</x:v>
+        <x:v>6월 이달 의 아이템</x:v>
       </x:c>
       <x:c r="K96" s="11" t="str">
-        <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
+        <x:v>document_sha256_8d15942b7c803029b811a23910302f2274bd00a85d68f3c8be8d1a6510122be6</x:v>
       </x:c>
       <x:c r="L96" s="11" t="str">
-        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
+        <x:v>chunk_sha256_6ca94020f0661c022cf19032640d142d7c07b4e1c0a29f21bc9bf908059ba95b</x:v>
       </x:c>
       <x:c r="M96" s="11" t="n">
-        <x:v>242</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="N96" s="11" t="n">
-        <x:v>257</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="O96" s="11" t="str">
-        <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
+        <x:v>https://df.nexon.com/community/news/seriashop/622</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="54" customHeight="1">
@@ -8498,28 +8498,29 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
-        <x:v>august_item_name</x:v>
+        <x:v>july_shop_price</x:v>
       </x:c>
       <x:c r="C97" s="11" t="str">
-        <x:v>unsupported</x:v>
+        <x:v>supported</x:v>
       </x:c>
       <x:c r="D97" s="11" t="str">
-        <x:v>8월 이달의 아이템</x:v>
+        <x:v>7월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
-        <x:v>item_name</x:v>
+        <x:v>shop_price</x:v>
       </x:c>
       <x:c r="F97" s="11" t="str">
-        <x:v>entity</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="G97" s="11" t="str">
-        <x:v>[]</x:v>
+        <x:v>[{"amount":40000000,"unit":"골드"}]</x:v>
       </x:c>
       <x:c r="H97" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I97" s="11" t="str">
-        <x:v>(공식 문서에서 근거 없음)</x:v>
+        <x:v>상점판매가
+4,000만 골드</x:v>
       </x:c>
       <x:c r="J97" s="11" t="str">
         <x:v>이달의 아이템</x:v>
@@ -8527,40 +8528,46 @@
       <x:c r="K97" s="11" t="str">
         <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
       </x:c>
-      <x:c r="L97" s="11"/>
-      <x:c r="M97" s="11"/>
-      <x:c r="N97" s="11"/>
+      <x:c r="L97" s="11" t="str">
+        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
+      </x:c>
+      <x:c r="M97" s="11" t="n">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="N97" s="11" t="n">
+        <x:v>257</x:v>
+      </x:c>
       <x:c r="O97" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="54" customHeight="1">
       <x:c r="A98" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>acquisition_method</x:v>
+        <x:v>august_item_name</x:v>
       </x:c>
       <x:c r="C98" s="11" t="str">
-        <x:v>supported</x:v>
+        <x:v>unsupported</x:v>
       </x:c>
       <x:c r="D98" s="11" t="str">
-        <x:v>이달의 아이템</x:v>
+        <x:v>8월 이달의 아이템</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
-        <x:v>acquisition_method</x:v>
+        <x:v>item_name</x:v>
       </x:c>
       <x:c r="F98" s="11" t="str">
-        <x:v>text</x:v>
+        <x:v>entity</x:v>
       </x:c>
       <x:c r="G98" s="11" t="str">
-        <x:v>["해방의 열쇠로 봉인된 자물쇠를 열어 확률적으로 획득"]</x:v>
+        <x:v>[]</x:v>
       </x:c>
       <x:c r="H98" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="11" t="str">
-        <x:v>세라샵에서 구매한 ‘해방의 열쇠’로 ‘봉인된 자물쇠’를 열어 특정 확률에 따라 이달의 아이템을 획득할 수 있습니다.</x:v>
+        <x:v>(공식 문서에서 근거 없음)</x:v>
       </x:c>
       <x:c r="J98" s="11" t="str">
         <x:v>이달의 아이템</x:v>
@@ -8568,26 +8575,67 @@
       <x:c r="K98" s="11" t="str">
         <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
       </x:c>
-      <x:c r="L98" s="11" t="str">
-        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
-      </x:c>
-      <x:c r="M98" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N98" s="11" t="n">
-        <x:v>83</x:v>
-      </x:c>
+      <x:c r="L98" s="11"/>
+      <x:c r="M98" s="11"/>
+      <x:c r="N98" s="11"/>
       <x:c r="O98" s="11" t="str">
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
     </x:row>
+    <x:row r="99" ht="54" customHeight="1">
+      <x:c r="A99" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="str">
+        <x:v>acquisition_method</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="str">
+        <x:v>supported</x:v>
+      </x:c>
+      <x:c r="D99" s="11" t="str">
+        <x:v>이달의 아이템</x:v>
+      </x:c>
+      <x:c r="E99" s="11" t="str">
+        <x:v>acquisition_method</x:v>
+      </x:c>
+      <x:c r="F99" s="11" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="G99" s="11" t="str">
+        <x:v>["해방의 열쇠로 봉인된 자물쇠를 열어 확률적으로 획득"]</x:v>
+      </x:c>
+      <x:c r="H99" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I99" s="11" t="str">
+        <x:v>세라샵에서 구매한 ‘해방의 열쇠’로 ‘봉인된 자물쇠’를 열어 특정 확률에 따라 이달의 아이템을 획득할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="J99" s="11" t="str">
+        <x:v>이달의 아이템</x:v>
+      </x:c>
+      <x:c r="K99" s="11" t="str">
+        <x:v>document_sha256_e1b41518d35b1284a3a07936b23f997653287b5b25426f6aca4cb04ac6eaa98e</x:v>
+      </x:c>
+      <x:c r="L99" s="11" t="str">
+        <x:v>chunk_sha256_d23a0df67a37d463f0221e3e9bfbd4fd8a65bd4b2577478c7573239523ef6043</x:v>
+      </x:c>
+      <x:c r="M99" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="N99" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="O99" s="11" t="str">
+        <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="C2:C98">
+  <x:conditionalFormatting sqref="C2:C99">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="unsupported"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15a43020be5244c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32a9654140444ad4"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/outputs/019f8a1b-d701-7662-81fe-3741d3277c70/typed_evidence_ref_generalization_review_64.xlsx
+++ b/outputs/019f8a1b-d701-7662-81fe-3741d3277c70/typed_evidence_ref_generalization_review_64.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9e349795f6134cb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="R1f9370a0fc084020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="3" r:id="R9dbf7b115bd54b15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" r:id="R30a8b18cccee4edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbf07dc729fb1406b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" r:id="Rac173db7bebf4dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="3" r:id="R18b4dc5b78fe4c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" r:id="R16f51206e6954103"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -517,7 +517,7 @@
       </x:c>
       <x:c r="B5" s="11" t="n">
         <x:f>COUNTIF(Review!M2:M65,"pending")</x:f>
-        <x:v>64</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -708,7 +708,7 @@
         <x:v>잠금 상태</x:v>
       </x:c>
       <x:c r="B22" s="11" t="str">
-        <x:v>64개 모두 pending_human_review</x:v>
+        <x:v>64개 모두 human_review_approved + SHA sealed</x:v>
       </x:c>
       <x:c r="C22" s="11"/>
       <x:c r="D22" s="11"/>
@@ -720,7 +720,7 @@
         <x:v>평가 실행</x:v>
       </x:c>
       <x:c r="B23" s="11" t="str">
-        <x:v>실행하지 않음</x:v>
+        <x:v>봉인본 one-shot 1회만 허용</x:v>
       </x:c>
       <x:c r="C23" s="11"/>
       <x:c r="D23" s="11"/>
@@ -732,7 +732,7 @@
         <x:v>승격 조건</x:v>
       </x:c>
       <x:c r="B24" s="11" t="str">
-        <x:v>사람 검수 완료 후 freeze SHA 생성</x:v>
+        <x:v>실행 후 자동 고정분모 지표를 그대로 보고</x:v>
       </x:c>
       <x:c r="C24" s="11"/>
       <x:c r="D24" s="11"/>
@@ -744,7 +744,7 @@
         <x:v>주의</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>현재 파일은 검수 패킷이며 독립 성능으로 주장할 수 없음</x:v>
+        <x:v>봉인 이후 질문·정답·근거 수정 및 재실행 금지</x:v>
       </x:c>
       <x:c r="C25" s="11"/>
       <x:c r="D25" s="11"/>
@@ -874,16 +874,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2927117</x:v>
       </x:c>
       <x:c r="L2" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M2" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N2" s="11"/>
-      <x:c r="O2" s="11"/>
-      <x:c r="P2" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N2" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O2" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P2" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q2" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R2" s="11"/>
     </x:row>
@@ -922,16 +928,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2926884</x:v>
       </x:c>
       <x:c r="L3" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M3" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N3" s="11"/>
-      <x:c r="O3" s="11"/>
-      <x:c r="P3" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N3" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O3" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P3" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q3" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R3" s="11"/>
     </x:row>
@@ -971,16 +983,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2924996</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M4" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N4" s="11"/>
-      <x:c r="O4" s="11"/>
-      <x:c r="P4" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N4" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O4" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P4" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q4" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R4" s="11"/>
     </x:row>
@@ -1020,16 +1038,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2923292</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M5" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N5" s="11"/>
-      <x:c r="O5" s="11"/>
-      <x:c r="P5" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N5" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O5" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P5" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q5" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R5" s="11"/>
     </x:row>
@@ -1068,16 +1092,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2926860</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M6" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N6" s="11"/>
-      <x:c r="O6" s="11"/>
-      <x:c r="P6" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N6" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O6" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P6" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q6" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R6" s="11"/>
     </x:row>
@@ -1116,16 +1146,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2923361</x:v>
       </x:c>
       <x:c r="L7" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M7" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N7" s="11"/>
-      <x:c r="O7" s="11"/>
-      <x:c r="P7" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N7" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O7" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P7" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q7" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R7" s="11"/>
     </x:row>
@@ -1165,16 +1201,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2926884</x:v>
       </x:c>
       <x:c r="L8" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M8" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N8" s="11"/>
-      <x:c r="O8" s="11"/>
-      <x:c r="P8" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N8" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O8" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P8" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q8" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R8" s="11"/>
     </x:row>
@@ -1213,16 +1255,22 @@
         <x:v>https://df.nexon.com/community/news/notice/2927710</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M9" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N9" s="11"/>
-      <x:c r="O9" s="11"/>
-      <x:c r="P9" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N9" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O9" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P9" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q9" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R9" s="11"/>
     </x:row>
@@ -1261,16 +1309,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927617</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M10" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N10" s="11"/>
-      <x:c r="O10" s="11"/>
-      <x:c r="P10" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N10" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O10" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P10" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q10" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R10" s="11"/>
     </x:row>
@@ -1309,16 +1363,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927913</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M11" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N11" s="11"/>
-      <x:c r="O11" s="11"/>
-      <x:c r="P11" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N11" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O11" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P11" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q11" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R11" s="11"/>
     </x:row>
@@ -1358,16 +1418,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927913</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M12" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N12" s="11"/>
-      <x:c r="O12" s="11"/>
-      <x:c r="P12" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N12" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O12" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P12" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q12" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R12" s="11"/>
     </x:row>
@@ -1407,16 +1473,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927522</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M13" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N13" s="11"/>
-      <x:c r="O13" s="11"/>
-      <x:c r="P13" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N13" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O13" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P13" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q13" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R13" s="11"/>
     </x:row>
@@ -1455,16 +1527,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927522</x:v>
       </x:c>
       <x:c r="L14" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M14" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N14" s="11"/>
-      <x:c r="O14" s="11"/>
-      <x:c r="P14" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N14" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O14" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P14" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q14" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R14" s="11"/>
     </x:row>
@@ -1503,16 +1581,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927122</x:v>
       </x:c>
       <x:c r="L15" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M15" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N15" s="11"/>
-      <x:c r="O15" s="11"/>
-      <x:c r="P15" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N15" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O15" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P15" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q15" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R15" s="11"/>
     </x:row>
@@ -1552,16 +1636,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927913</x:v>
       </x:c>
       <x:c r="L16" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M16" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N16" s="11"/>
-      <x:c r="O16" s="11"/>
-      <x:c r="P16" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N16" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O16" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P16" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q16" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R16" s="11"/>
     </x:row>
@@ -1600,16 +1690,22 @@
         <x:v>https://df.nexon.com/community/news/update/2927913</x:v>
       </x:c>
       <x:c r="L17" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M17" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N17" s="11"/>
-      <x:c r="O17" s="11"/>
-      <x:c r="P17" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N17" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O17" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P17" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q17" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R17" s="11"/>
     </x:row>
@@ -1648,16 +1744,22 @@
         <x:v>https://df.nexon.com/pg/oceanmiracle</x:v>
       </x:c>
       <x:c r="L18" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M18" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N18" s="11"/>
-      <x:c r="O18" s="11"/>
-      <x:c r="P18" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N18" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O18" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P18" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q18" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R18" s="11"/>
     </x:row>
@@ -1696,16 +1798,22 @@
         <x:v>https://df.nexon.com/pg/summerblossom</x:v>
       </x:c>
       <x:c r="L19" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M19" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N19" s="11"/>
-      <x:c r="O19" s="11"/>
-      <x:c r="P19" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N19" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O19" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P19" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q19" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R19" s="11"/>
     </x:row>
@@ -1745,16 +1853,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/626</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M20" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N20" s="11"/>
-      <x:c r="O20" s="11"/>
-      <x:c r="P20" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N20" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O20" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P20" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q20" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R20" s="11"/>
     </x:row>
@@ -1794,16 +1908,22 @@
         <x:v>https://df.nexon.com/pg/michaelapreviewlive</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M21" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N21" s="11"/>
-      <x:c r="O21" s="11"/>
-      <x:c r="P21" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N21" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O21" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P21" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q21" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R21" s="11"/>
     </x:row>
@@ -1843,16 +1963,22 @@
         <x:v>https://df.nexon.com/pg/newcharacterpkg</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M22" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N22" s="11"/>
-      <x:c r="O22" s="11"/>
-      <x:c r="P22" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N22" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O22" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P22" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q22" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R22" s="11"/>
     </x:row>
@@ -1891,16 +2017,22 @@
         <x:v>https://df.nexon.com/pg/butterflycombo</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M23" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N23" s="11"/>
-      <x:c r="O23" s="11"/>
-      <x:c r="P23" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N23" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O23" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P23" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q23" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R23" s="11"/>
     </x:row>
@@ -1940,16 +2072,22 @@
         <x:v>https://df.nexon.com/pr/newfacewithnxp</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M24" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N24" s="11"/>
-      <x:c r="O24" s="11"/>
-      <x:c r="P24" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N24" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O24" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P24" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q24" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R24" s="11"/>
     </x:row>
@@ -1988,16 +2126,22 @@
         <x:v>https://df.nexon.com/pr/2026newchargift</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M25" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N25" s="11"/>
-      <x:c r="O25" s="11"/>
-      <x:c r="P25" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N25" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O25" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P25" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q25" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R25" s="11"/>
     </x:row>
@@ -2037,16 +2181,22 @@
         <x:v>https://df.nexon.com/guide?no=1326</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M26" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N26" s="11"/>
-      <x:c r="O26" s="11"/>
-      <x:c r="P26" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N26" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O26" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P26" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q26" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R26" s="11"/>
     </x:row>
@@ -2085,16 +2235,22 @@
         <x:v>https://df.nexon.com/guide?no=1286</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M27" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N27" s="11"/>
-      <x:c r="O27" s="11"/>
-      <x:c r="P27" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N27" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O27" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P27" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q27" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R27" s="11"/>
     </x:row>
@@ -2134,16 +2290,22 @@
         <x:v>https://df.nexon.com/guide?no=1286</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M28" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N28" s="11"/>
-      <x:c r="O28" s="11"/>
-      <x:c r="P28" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N28" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O28" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P28" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q28" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R28" s="11"/>
     </x:row>
@@ -2183,16 +2345,22 @@
         <x:v>https://df.nexon.com/guide?no=1270</x:v>
       </x:c>
       <x:c r="L29" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M29" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N29" s="11"/>
-      <x:c r="O29" s="11"/>
-      <x:c r="P29" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N29" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O29" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P29" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q29" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R29" s="11"/>
     </x:row>
@@ -2232,16 +2400,22 @@
         <x:v>https://df.nexon.com/guide?no=1292</x:v>
       </x:c>
       <x:c r="L30" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M30" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N30" s="11"/>
-      <x:c r="O30" s="11"/>
-      <x:c r="P30" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N30" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O30" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P30" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q30" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R30" s="11"/>
     </x:row>
@@ -2280,16 +2454,22 @@
         <x:v>https://df.nexon.com/guide?no=1494</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M31" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N31" s="11"/>
-      <x:c r="O31" s="11"/>
-      <x:c r="P31" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N31" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O31" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P31" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q31" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R31" s="11"/>
     </x:row>
@@ -2329,16 +2509,22 @@
         <x:v>https://df.nexon.com/guide?no=1280</x:v>
       </x:c>
       <x:c r="L32" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M32" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N32" s="11"/>
-      <x:c r="O32" s="11"/>
-      <x:c r="P32" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N32" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O32" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P32" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q32" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R32" s="11"/>
     </x:row>
@@ -2377,16 +2563,22 @@
         <x:v>https://df.nexon.com/guide?no=1526</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M33" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N33" s="11"/>
-      <x:c r="O33" s="11"/>
-      <x:c r="P33" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N33" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O33" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P33" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q33" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R33" s="11"/>
     </x:row>
@@ -2425,16 +2617,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=4950</x:v>
       </x:c>
       <x:c r="L34" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M34" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N34" s="11"/>
-      <x:c r="O34" s="11"/>
-      <x:c r="P34" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N34" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O34" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P34" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q34" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R34" s="11"/>
     </x:row>
@@ -2473,16 +2671,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=4901</x:v>
       </x:c>
       <x:c r="L35" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M35" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N35" s="11"/>
-      <x:c r="O35" s="11"/>
-      <x:c r="P35" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N35" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O35" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P35" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q35" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R35" s="11"/>
     </x:row>
@@ -2522,16 +2726,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=5001</x:v>
       </x:c>
       <x:c r="L36" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M36" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N36" s="11"/>
-      <x:c r="O36" s="11"/>
-      <x:c r="P36" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N36" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O36" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P36" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q36" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R36" s="11"/>
     </x:row>
@@ -2571,16 +2781,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=5630</x:v>
       </x:c>
       <x:c r="L37" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M37" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N37" s="11"/>
-      <x:c r="O37" s="11"/>
-      <x:c r="P37" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N37" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O37" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P37" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q37" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R37" s="11"/>
     </x:row>
@@ -2620,16 +2836,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=4994</x:v>
       </x:c>
       <x:c r="L38" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M38" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N38" s="11"/>
-      <x:c r="O38" s="11"/>
-      <x:c r="P38" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N38" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O38" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P38" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q38" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R38" s="11"/>
     </x:row>
@@ -2669,16 +2891,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=4923</x:v>
       </x:c>
       <x:c r="L39" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M39" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N39" s="11"/>
-      <x:c r="O39" s="11"/>
-      <x:c r="P39" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N39" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O39" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P39" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q39" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R39" s="11"/>
     </x:row>
@@ -2718,16 +2946,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=5951</x:v>
       </x:c>
       <x:c r="L40" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M40" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N40" s="11"/>
-      <x:c r="O40" s="11"/>
-      <x:c r="P40" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N40" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O40" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P40" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q40" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R40" s="11"/>
     </x:row>
@@ -2766,16 +3000,22 @@
         <x:v>https://df.nexon.com/customer/faq?faq_no=2785</x:v>
       </x:c>
       <x:c r="L41" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M41" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N41" s="11"/>
-      <x:c r="O41" s="11"/>
-      <x:c r="P41" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N41" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O41" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P41" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q41" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R41" s="11"/>
     </x:row>
@@ -2814,16 +3054,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L42" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M42" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N42" s="11"/>
-      <x:c r="O42" s="11"/>
-      <x:c r="P42" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N42" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O42" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P42" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q42" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R42" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -2864,16 +3110,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L43" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M43" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N43" s="11"/>
-      <x:c r="O43" s="11"/>
-      <x:c r="P43" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N43" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O43" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P43" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q43" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R43" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -2915,16 +3167,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L44" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M44" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N44" s="11"/>
-      <x:c r="O44" s="11"/>
-      <x:c r="P44" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N44" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O44" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P44" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q44" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R44" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -2966,16 +3224,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L45" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M45" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N45" s="11"/>
-      <x:c r="O45" s="11"/>
-      <x:c r="P45" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N45" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O45" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P45" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q45" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R45" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -3017,16 +3281,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L46" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M46" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N46" s="11"/>
-      <x:c r="O46" s="11"/>
-      <x:c r="P46" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N46" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O46" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P46" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q46" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R46" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -3067,16 +3337,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L47" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M47" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N47" s="11"/>
-      <x:c r="O47" s="11"/>
-      <x:c r="P47" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N47" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O47" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P47" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q47" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R47" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -3118,16 +3394,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L48" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M48" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N48" s="11"/>
-      <x:c r="O48" s="11"/>
-      <x:c r="P48" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N48" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O48" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P48" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q48" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R48" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -3168,16 +3450,22 @@
         <x:v>https://df.nexon.com/customer/policy/home?revision=2026-03-15&amp;type=1</x:v>
       </x:c>
       <x:c r="L49" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M49" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N49" s="11"/>
-      <x:c r="O49" s="11"/>
-      <x:c r="P49" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N49" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O49" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P49" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q49" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R49" s="11" t="str">
         <x:v>운영정책은 현재 공식 revision이 한 개뿐이므로 parent 재사용을 허용하되 신규 관계와 질문만 사용합니다.</x:v>
@@ -3218,16 +3506,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/378</x:v>
       </x:c>
       <x:c r="L50" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M50" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N50" s="11"/>
-      <x:c r="O50" s="11"/>
-      <x:c r="P50" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N50" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O50" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P50" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q50" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R50" s="11"/>
     </x:row>
@@ -3266,16 +3560,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/634</x:v>
       </x:c>
       <x:c r="L51" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M51" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N51" s="11"/>
-      <x:c r="O51" s="11"/>
-      <x:c r="P51" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N51" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O51" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P51" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q51" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R51" s="11"/>
     </x:row>
@@ -3315,16 +3615,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/647</x:v>
       </x:c>
       <x:c r="L52" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M52" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N52" s="11"/>
-      <x:c r="O52" s="11"/>
-      <x:c r="P52" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N52" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O52" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P52" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q52" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R52" s="11"/>
     </x:row>
@@ -3365,16 +3671,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
       </x:c>
       <x:c r="L53" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M53" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N53" s="11"/>
-      <x:c r="O53" s="11"/>
-      <x:c r="P53" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N53" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O53" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P53" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q53" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R53" s="11"/>
     </x:row>
@@ -3414,16 +3726,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/634</x:v>
       </x:c>
       <x:c r="L54" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M54" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N54" s="11"/>
-      <x:c r="O54" s="11"/>
-      <x:c r="P54" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N54" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O54" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P54" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q54" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R54" s="11"/>
     </x:row>
@@ -3462,16 +3780,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/647</x:v>
       </x:c>
       <x:c r="L55" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M55" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N55" s="11"/>
-      <x:c r="O55" s="11"/>
-      <x:c r="P55" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N55" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O55" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P55" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q55" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R55" s="11"/>
     </x:row>
@@ -3511,16 +3835,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
       </x:c>
       <x:c r="L56" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M56" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N56" s="11"/>
-      <x:c r="O56" s="11"/>
-      <x:c r="P56" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N56" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O56" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P56" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q56" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R56" s="11"/>
     </x:row>
@@ -3559,16 +3889,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/641</x:v>
       </x:c>
       <x:c r="L57" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M57" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N57" s="11"/>
-      <x:c r="O57" s="11"/>
-      <x:c r="P57" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N57" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O57" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P57" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q57" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R57" s="11"/>
     </x:row>
@@ -3607,16 +3943,22 @@
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
       <x:c r="L58" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M58" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N58" s="11"/>
-      <x:c r="O58" s="11"/>
-      <x:c r="P58" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N58" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O58" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P58" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q58" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R58" s="11" t="str">
         <x:v>이달의 아이템은 현재 월 revision이 한 개뿐이므로 신규 관계와 질문에 한해 parent 재사용을 허용합니다.</x:v>
@@ -3657,16 +3999,22 @@
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
       <x:c r="L59" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M59" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N59" s="11"/>
-      <x:c r="O59" s="11"/>
-      <x:c r="P59" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N59" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O59" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P59" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q59" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R59" s="11" t="str">
         <x:v>이달의 아이템은 현재 월 revision이 한 개뿐이므로 신규 관계와 질문에 한해 parent 재사용을 허용합니다.</x:v>
@@ -3707,16 +4055,22 @@
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
       <x:c r="L60" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M60" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N60" s="11"/>
-      <x:c r="O60" s="11"/>
-      <x:c r="P60" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N60" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O60" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P60" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q60" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R60" s="11" t="str">
         <x:v>이달의 아이템은 현재 월 revision이 한 개뿐이므로 신규 관계와 질문에 한해 parent 재사용을 허용합니다.</x:v>
@@ -3758,16 +4112,22 @@
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
       <x:c r="L61" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M61" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N61" s="11"/>
-      <x:c r="O61" s="11"/>
-      <x:c r="P61" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N61" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O61" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P61" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q61" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R61" s="11" t="str">
         <x:v>이달의 아이템은 현재 월 revision이 한 개뿐이므로 신규 관계와 질문에 한해 parent 재사용을 허용합니다.</x:v>
@@ -3809,16 +4169,22 @@
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
       <x:c r="L62" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M62" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N62" s="11"/>
-      <x:c r="O62" s="11"/>
-      <x:c r="P62" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N62" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O62" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P62" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q62" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R62" s="11" t="str">
         <x:v>이달의 아이템은 현재 월 revision이 한 개뿐이므로 신규 관계와 질문에 한해 parent 재사용을 허용합니다.</x:v>
@@ -3859,16 +4225,22 @@
         <x:v>https://df.nexon.com/community/news/seriashop/622</x:v>
       </x:c>
       <x:c r="L63" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M63" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N63" s="11"/>
-      <x:c r="O63" s="11"/>
-      <x:c r="P63" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N63" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O63" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P63" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q63" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R63" s="11" t="str">
         <x:v>월별 공식 revision 비교를 위해 과거 6월 parent를 사용하며 질문과 관계는 신규입니다.</x:v>
@@ -3910,16 +4282,22 @@
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
       <x:c r="L64" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M64" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N64" s="11"/>
-      <x:c r="O64" s="11"/>
-      <x:c r="P64" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N64" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O64" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P64" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q64" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R64" s="11" t="str">
         <x:v>이달의 아이템은 현재 월 revision이 한 개뿐이므로 신규 관계와 질문에 한해 parent 재사용을 허용합니다.</x:v>
@@ -3960,16 +4338,22 @@
         <x:v>https://df.nexon.com/community/news/monthlyitem</x:v>
       </x:c>
       <x:c r="L65" s="11" t="str">
-        <x:v>draft_complete_pending_human_review</x:v>
+        <x:v>human_review_approved_sealed</x:v>
       </x:c>
       <x:c r="M65" s="11" t="str">
-        <x:v>pending</x:v>
-      </x:c>
-      <x:c r="N65" s="11"/>
-      <x:c r="O65" s="11"/>
-      <x:c r="P65" s="11"/>
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="N65" s="11" t="str">
+        <x:v>kimdh</x:v>
+      </x:c>
+      <x:c r="O65" s="11" t="n">
+        <x:v>46227.5043946875</x:v>
+      </x:c>
+      <x:c r="P65" s="11" t="str">
+        <x:v>사용자가 64문항 전체 감수 완료 및 one-shot 봉인을 승인함</x:v>
+      </x:c>
       <x:c r="Q65" s="20" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R65" s="11" t="str">
         <x:v>이달의 아이템은 현재 월 revision이 한 개뿐이므로 신규 관계와 질문에 한해 parent 재사용을 허용합니다.</x:v>
@@ -3989,7 +4373,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8e765ffcda243cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd2f05e65b7343a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8635,7 +9019,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32a9654140444ad4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R487f102a650c4e30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8689,7 +9073,7 @@
         <x:v>현재 상태</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>64/64 draft_complete_pending_human_review</x:v>
+        <x:v>64/64 human_review_approved_sealed</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
@@ -8697,7 +9081,7 @@
         <x:v>평가 가능 여부</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>불가 — execution_allowed=false</x:v>
+        <x:v>가능 — 봉인본 one-shot 1회만</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
@@ -8745,7 +9129,7 @@
         <x:v>주의</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>문항 작성 후 아직 검색·reranker·Qwen3·verifier를 실행하지 않음</x:v>
+        <x:v>봉인 이후 질문·정답·근거 수정 및 재실행 금지</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
@@ -8753,7 +9137,7 @@
         <x:v>다음 단계</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>사람 검수 완료 → approved 60개 이상 확인 → freeze 및 SHA 기록 → 최초 A/B</x:v>
+        <x:v>자동 고정분모 지표와 정직보류 false-full을 보고</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
